--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60261-2024</t>
+          <t>A 53422-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45642</v>
+        <v>45229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -861,147 +861,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 60261-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45642</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 53422-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44475</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44746</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>44472</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45366</v>
+        <v>44903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45386</v>
+        <v>44977</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1809,14 +1809,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45590</v>
+        <v>45789</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45155</v>
+        <v>45278</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46070</v>
+        <v>45016</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2018,7 +2018,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45894</v>
+        <v>45635</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45016</v>
+        <v>45051</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 41381-2025</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45898</v>
+        <v>45173</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45901</v>
+        <v>45436</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2320,14 +2320,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45182</v>
+        <v>45894</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45852</v>
+        <v>44903</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45852</v>
+        <v>44903</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45905</v>
+        <v>45901</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 41381-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45859</v>
+        <v>45898</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45910</v>
+        <v>45905</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46076</v>
+        <v>46042</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2831,14 +2831,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46076</v>
+        <v>45910</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2911,7 +2911,7 @@
         <v>45915</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 38036-2025</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45881</v>
+        <v>45673</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45642</v>
+        <v>46059</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45642</v>
+        <v>46059</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45229</v>
+        <v>45188</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45933</v>
+        <v>45852</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45642</v>
+        <v>46064</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44977</v>
+        <v>45852</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3478,7 +3478,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45847</v>
+        <v>45642</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46086</v>
+        <v>45229</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3624,7 +3624,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46086</v>
+        <v>45859</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>9.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46090</v>
+        <v>45642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3770,7 +3770,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46090</v>
+        <v>45642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46099</v>
+        <v>46070</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46111</v>
+        <v>45933</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3999,14 +3999,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46112</v>
+        <v>46076</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45965</v>
+        <v>46076</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45980</v>
+        <v>45847</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 38036-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45980</v>
+        <v>45881</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46128</v>
+        <v>46086</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46133</v>
+        <v>46086</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44903</v>
+        <v>46090</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4500,7 +4500,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46042</v>
+        <v>46090</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4573,7 +4573,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45673</v>
+        <v>45155</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46059</v>
+        <v>46099</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46059</v>
+        <v>46112</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46064</v>
+        <v>45590</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 25009-2023</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45085</v>
+        <v>46111</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45574</v>
+        <v>45965</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45541</v>
+        <v>45386</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46154</v>
+        <v>46128</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46154</v>
+        <v>46133</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46155</v>
+        <v>45980</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>10.4</v>
+        <v>2.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45653</v>
+        <v>45980</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45155</v>
+        <v>45574</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45188</v>
+        <v>44977</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44903</v>
+        <v>45155</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5609,10 +5609,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44903</v>
+        <v>45761</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45436</v>
+        <v>45761</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46243</v>
+        <v>45761</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5814,7 +5814,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44899</v>
+        <v>44497</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44977</v>
+        <v>46155</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>10.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44497</v>
+        <v>46154</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6033,7 +6033,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6047,10 +6047,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45436</v>
+        <v>46154</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6106,7 +6106,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45386</v>
+        <v>45436</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6179,7 +6179,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45164</v>
+        <v>46243</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6252,7 +6252,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44929</v>
+        <v>46157</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6342,7 +6342,7 @@
         <v>46261</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44977</v>
+        <v>44929</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.3</v>
+        <v>4.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6471,7 +6471,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45761</v>
+        <v>46266</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6500,8 +6500,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6544,7 +6549,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6558,10 +6563,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45761</v>
+        <v>46230</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6574,7 +6579,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6617,7 +6622,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6631,10 +6636,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45761</v>
+        <v>45164</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6647,7 +6652,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6690,7 +6695,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6704,10 +6709,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46157</v>
+        <v>45653</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6720,7 +6725,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6763,7 +6768,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6777,10 +6782,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46266</v>
+        <v>45436</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6792,13 +6797,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6841,7 +6841,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6855,10 +6855,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45386</v>
+        <v>44977</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6914,7 +6914,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 25009-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6924,14 +6924,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45319</v>
+        <v>45085</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6997,14 +6997,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46230</v>
+        <v>45182</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7060,7 +7060,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45293</v>
+        <v>45386</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7133,7 +7133,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7143,14 +7143,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45789</v>
+        <v>45366</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7206,7 +7206,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7216,14 +7216,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45635</v>
+        <v>45319</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7279,7 +7279,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45173</v>
+        <v>45541</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7352,7 +7352,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45051</v>
+        <v>45386</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7425,7 +7425,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7439,10 +7439,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45278</v>
+        <v>44899</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7498,7 +7498,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7512,10 +7512,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45436</v>
+        <v>45293</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
         <v>45006</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 53422-2023</t>
+          <t>A 60261-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45229</v>
+        <v>45642</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -861,147 +861,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 53422-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 60261-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45642</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44475</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44746</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 54313-2021</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44472</v>
+        <v>45155</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1580,7 +1580,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 60972-2021</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44497</v>
+        <v>45188</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 54313-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44903</v>
+        <v>44472</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 60972-2021</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1736,14 +1736,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44977</v>
+        <v>44497</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 38036-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1809,14 +1809,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45789</v>
+        <v>45881</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45278</v>
+        <v>45366</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45016</v>
+        <v>44903</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2018,7 +2018,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45635</v>
+        <v>44903</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45051</v>
+        <v>45386</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.2</v>
+        <v>8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45173</v>
+        <v>46086</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45436</v>
+        <v>46086</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45894</v>
+        <v>46090</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44903</v>
+        <v>45894</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44903</v>
+        <v>46090</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 41381-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45901</v>
+        <v>45898</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 41381-2025</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45898</v>
+        <v>45901</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45905</v>
+        <v>46099</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46042</v>
+        <v>45905</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2838,7 +2838,7 @@
         <v>45910</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45915</v>
+        <v>45590</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45673</v>
+        <v>45915</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46059</v>
+        <v>46111</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46059</v>
+        <v>46112</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45188</v>
+        <v>45155</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45852</v>
+        <v>45436</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46064</v>
+        <v>45642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45852</v>
+        <v>46128</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3495,7 +3495,7 @@
         <v>45642</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>45229</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45859</v>
+        <v>45933</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3714,7 +3714,7 @@
         <v>45642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3770,7 +3770,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45642</v>
+        <v>45847</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46070</v>
+        <v>46133</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45933</v>
+        <v>45016</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46076</v>
+        <v>45182</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46076</v>
+        <v>45965</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45847</v>
+        <v>44899</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38036-2025</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45881</v>
+        <v>45980</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46086</v>
+        <v>45980</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46086</v>
+        <v>44977</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>9.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46090</v>
+        <v>44497</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4500,7 +4500,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46090</v>
+        <v>44977</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4573,7 +4573,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45155</v>
+        <v>46154</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46099</v>
+        <v>46154</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46112</v>
+        <v>46155</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>10.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45590</v>
+        <v>46042</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46111</v>
+        <v>45673</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45965</v>
+        <v>45436</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45386</v>
+        <v>44903</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46128</v>
+        <v>46059</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46133</v>
+        <v>46059</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45980</v>
+        <v>46064</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45980</v>
+        <v>46070</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45574</v>
+        <v>46076</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5459,14 +5459,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44977</v>
+        <v>46076</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45155</v>
+        <v>45386</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5609,10 +5609,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45761</v>
+        <v>45164</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45761</v>
+        <v>46243</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45761</v>
+        <v>44929</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5814,7 +5814,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44497</v>
+        <v>44977</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5887,7 +5887,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46155</v>
+        <v>45761</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>10.4</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46154</v>
+        <v>45761</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6033,7 +6033,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6047,10 +6047,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46154</v>
+        <v>45761</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6106,7 +6106,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 25009-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45436</v>
+        <v>45085</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6179,7 +6179,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46243</v>
+        <v>45574</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6252,7 +6252,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46157</v>
+        <v>45541</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6325,7 +6325,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46261</v>
+        <v>45653</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6398,7 +6398,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44929</v>
+        <v>46261</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6471,7 +6471,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46266</v>
+        <v>46157</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6500,13 +6500,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6549,7 +6544,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6563,10 +6558,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46230</v>
+        <v>45386</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6579,7 +6574,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6622,7 +6617,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6632,14 +6627,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45164</v>
+        <v>45319</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6652,7 +6647,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6695,7 +6690,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6709,10 +6704,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45653</v>
+        <v>46266</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6724,8 +6719,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6768,7 +6768,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6782,10 +6782,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45436</v>
+        <v>46230</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6841,7 +6841,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6855,10 +6855,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44977</v>
+        <v>45293</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6914,7 +6914,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 25009-2023</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6924,14 +6924,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45085</v>
+        <v>45789</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6997,14 +6997,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45182</v>
+        <v>45635</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7060,7 +7060,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45386</v>
+        <v>45173</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7133,7 +7133,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45366</v>
+        <v>45051</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7206,7 +7206,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7216,14 +7216,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45319</v>
+        <v>45278</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7279,7 +7279,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45541</v>
+        <v>45436</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7352,7 +7352,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45386</v>
+        <v>45852</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7425,7 +7425,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7439,10 +7439,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44899</v>
+        <v>45852</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7498,7 +7498,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7512,10 +7512,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45293</v>
+        <v>45859</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
         <v>45006</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60261-2024</t>
+          <t>A 53422-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45642</v>
+        <v>45229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -861,147 +861,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 60261-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45642</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 53422-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44475</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44746</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 54313-2021</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45155</v>
+        <v>44472</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1580,7 +1580,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 60972-2021</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45188</v>
+        <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 54313-2021</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44472</v>
+        <v>44903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60972-2021</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1736,14 +1736,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44497</v>
+        <v>44977</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 38036-2025</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45881</v>
+        <v>45016</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45366</v>
+        <v>45051</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44903</v>
+        <v>45173</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2018,7 +2018,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2035,7 +2035,7 @@
         <v>44903</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45386</v>
+        <v>44903</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46086</v>
+        <v>45436</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46086</v>
+        <v>45894</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>9.199999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46090</v>
+        <v>45901</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 41381-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45894</v>
+        <v>45898</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46090</v>
+        <v>45905</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41381-2025</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45898</v>
+        <v>45188</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45901</v>
+        <v>45910</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46099</v>
+        <v>45915</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45905</v>
+        <v>45852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45910</v>
+        <v>45852</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45590</v>
+        <v>45859</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45915</v>
+        <v>45642</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46111</v>
+        <v>45229</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46112</v>
+        <v>45642</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45155</v>
+        <v>45642</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45436</v>
+        <v>45933</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45642</v>
+        <v>46042</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46128</v>
+        <v>45847</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3478,7 +3478,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 38036-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45642</v>
+        <v>45881</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45229</v>
+        <v>45155</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3624,7 +3624,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45933</v>
+        <v>45673</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45642</v>
+        <v>45590</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3770,7 +3770,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45847</v>
+        <v>46059</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46133</v>
+        <v>46059</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45016</v>
+        <v>45386</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3999,14 +3999,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45182</v>
+        <v>45965</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45965</v>
+        <v>46064</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44899</v>
+        <v>46070</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4225,7 +4225,7 @@
         <v>45980</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4298,7 +4298,7 @@
         <v>45980</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4364,14 +4364,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44977</v>
+        <v>46076</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44497</v>
+        <v>46076</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4500,7 +4500,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44977</v>
+        <v>45574</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4573,7 +4573,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46154</v>
+        <v>44977</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46154</v>
+        <v>46086</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46155</v>
+        <v>46086</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>10.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46042</v>
+        <v>46090</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45673</v>
+        <v>46090</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45436</v>
+        <v>45155</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44903</v>
+        <v>46099</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46059</v>
+        <v>45761</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46059</v>
+        <v>45761</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46064</v>
+        <v>45761</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46070</v>
+        <v>44497</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46076</v>
+        <v>46112</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5459,14 +5459,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46076</v>
+        <v>46111</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45386</v>
+        <v>45436</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5609,10 +5609,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45164</v>
+        <v>46128</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46243</v>
+        <v>46133</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5758,7 +5758,7 @@
         <v>44929</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44977</v>
+        <v>45164</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5887,7 +5887,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45761</v>
+        <v>46155</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>10.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45761</v>
+        <v>46154</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6033,7 +6033,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6047,10 +6047,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45761</v>
+        <v>45653</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6106,7 +6106,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 25009-2023</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45085</v>
+        <v>46154</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6179,7 +6179,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45574</v>
+        <v>45436</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6252,7 +6252,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45541</v>
+        <v>44977</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6325,7 +6325,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 25009-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45653</v>
+        <v>45085</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6398,7 +6398,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46261</v>
+        <v>46243</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6471,7 +6471,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6481,14 +6481,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46157</v>
+        <v>45182</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6544,7 +6544,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6561,7 +6561,7 @@
         <v>45386</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6617,7 +6617,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6627,14 +6627,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45319</v>
+        <v>46157</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6690,7 +6690,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6704,10 +6704,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46266</v>
+        <v>46261</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6719,13 +6719,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6768,7 +6763,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6782,10 +6777,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46230</v>
+        <v>45366</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6798,7 +6793,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6841,7 +6836,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6855,10 +6850,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45293</v>
+        <v>46266</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6870,8 +6865,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6914,7 +6914,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45789</v>
+        <v>45319</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45635</v>
+        <v>45541</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7060,7 +7060,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45173</v>
+        <v>46230</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7133,7 +7133,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45051</v>
+        <v>45386</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7206,7 +7206,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7220,10 +7220,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45278</v>
+        <v>44899</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7279,7 +7279,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45436</v>
+        <v>45293</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7352,7 +7352,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7362,14 +7362,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45852</v>
+        <v>45789</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7425,7 +7425,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7439,10 +7439,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45852</v>
+        <v>45278</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7498,7 +7498,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7512,10 +7512,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45859</v>
+        <v>45635</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
         <v>45006</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 53422-2023</t>
+          <t>A 60261-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45229</v>
+        <v>45642</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -861,151 +861,151 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 53422-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 60261-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45642</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 61174-2025</t>
+          <t>A 5311-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46000</v>
+        <v>44594</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1044,13 +1044,13 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1062,156 +1062,156 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 5311-2022 artfynd.xlsx", "A 5311-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 5311-2022 karta.png", "A 5311-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 5311-2022 georefererad karta.tif", "A 5311-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 5311-2022 FSC-klagomål.docx", "A 5311-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 5311-2022 FSC-klagomål mail.docx", "A 5311-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 5311-2022 tillsynsbegäran.docx", "A 5311-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 5311-2022 tillsynsbegäran mail.docx", "A 5311-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 61174-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46000</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Nordbjörnbär</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 61174-2025 artfynd.xlsx", "A 61174-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 61174-2025 karta.png", "A 61174-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 61174-2025 georefererad karta.tif", "A 61174-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 61174-2025 FSC-klagomål.docx", "A 61174-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 61174-2025 FSC-klagomål mail.docx", "A 61174-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 61174-2025 tillsynsbegäran.docx", "A 61174-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 61174-2025 tillsynsbegäran mail.docx", "A 61174-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 5311-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44594</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 5311-2022 artfynd.xlsx", "A 5311-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 5311-2022 karta.png", "A 5311-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 5311-2022 georefererad karta.tif", "A 5311-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 5311-2022 FSC-klagomål.docx", "A 5311-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 5311-2022 FSC-klagomål mail.docx", "A 5311-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 5311-2022 tillsynsbegäran.docx", "A 5311-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 5311-2022 tillsynsbegäran mail.docx", "A 5311-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44475</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44746</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>44472</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44903</v>
+        <v>45366</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44977</v>
+        <v>45386</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45016</v>
+        <v>45590</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45051</v>
+        <v>46070</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45173</v>
+        <v>45155</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2018,7 +2018,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44903</v>
+        <v>46076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2101,14 +2101,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44903</v>
+        <v>46076</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45436</v>
+        <v>46086</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45894</v>
+        <v>46086</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45901</v>
+        <v>45016</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 41381-2025</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45898</v>
+        <v>46090</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45905</v>
+        <v>46090</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2539,14 +2539,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45188</v>
+        <v>45182</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45910</v>
+        <v>46099</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45915</v>
+        <v>45852</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
         <v>45852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45852</v>
+        <v>45859</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45859</v>
+        <v>46111</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45642</v>
+        <v>46112</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45229</v>
+        <v>45894</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 38036-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45642</v>
+        <v>45881</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45642</v>
+        <v>44977</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 41381-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45933</v>
+        <v>45898</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46042</v>
+        <v>46128</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45847</v>
+        <v>45901</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3478,7 +3478,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38036-2025</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45881</v>
+        <v>46133</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45155</v>
+        <v>45905</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3624,7 +3624,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45673</v>
+        <v>45910</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45590</v>
+        <v>45915</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3770,7 +3770,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46059</v>
+        <v>45642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46059</v>
+        <v>44903</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45386</v>
+        <v>45642</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>8</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45965</v>
+        <v>46154</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46064</v>
+        <v>46154</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46070</v>
+        <v>45229</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45980</v>
+        <v>45933</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45980</v>
+        <v>45642</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4364,14 +4364,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46076</v>
+        <v>46155</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.8</v>
+        <v>10.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46076</v>
+        <v>45847</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4500,7 +4500,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 25009-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45574</v>
+        <v>45085</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4573,7 +4573,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44977</v>
+        <v>45574</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46086</v>
+        <v>45541</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46086</v>
+        <v>45965</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>9.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46090</v>
+        <v>46243</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46090</v>
+        <v>45653</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45155</v>
+        <v>45980</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46099</v>
+        <v>45980</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45761</v>
+        <v>45155</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45761</v>
+        <v>45188</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45761</v>
+        <v>44903</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44497</v>
+        <v>44903</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46112</v>
+        <v>46261</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46111</v>
+        <v>46157</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45436</v>
+        <v>46266</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5551,8 +5551,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5595,7 +5600,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5609,10 +5614,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46128</v>
+        <v>46230</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5625,7 +5630,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5668,7 +5673,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5682,10 +5687,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46133</v>
+        <v>45436</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5698,7 +5703,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5741,7 +5746,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5755,10 +5760,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44929</v>
+        <v>44899</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5771,7 +5776,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5814,7 +5819,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5828,10 +5833,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45164</v>
+        <v>44977</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5844,7 +5849,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5887,7 +5892,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5901,10 +5906,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46155</v>
+        <v>44497</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5917,7 +5922,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>10.4</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5960,7 +5965,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5974,10 +5979,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46154</v>
+        <v>46042</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5990,7 +5995,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6033,7 +6038,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6047,10 +6052,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45653</v>
+        <v>45436</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6063,7 +6068,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6106,7 +6111,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6120,10 +6125,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46154</v>
+        <v>45673</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6136,7 +6141,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6179,7 +6184,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6193,10 +6198,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45436</v>
+        <v>45386</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6209,7 +6214,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6252,7 +6257,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6266,10 +6271,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44977</v>
+        <v>45164</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6282,7 +6287,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6325,7 +6330,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 25009-2023</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6339,10 +6344,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45085</v>
+        <v>46059</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6355,7 +6360,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6398,7 +6403,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6412,10 +6417,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46243</v>
+        <v>46059</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6428,7 +6433,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6471,7 +6476,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6481,14 +6486,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45182</v>
+        <v>46064</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6501,7 +6506,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6544,7 +6549,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6558,10 +6563,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45386</v>
+        <v>44929</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6574,7 +6579,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6617,7 +6622,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6631,10 +6636,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46157</v>
+        <v>44977</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6647,7 +6652,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.5</v>
+        <v>0.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6690,7 +6695,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6704,10 +6709,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46261</v>
+        <v>45761</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6720,7 +6725,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6763,7 +6768,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6777,10 +6782,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45366</v>
+        <v>45761</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6793,7 +6798,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6836,7 +6841,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6850,10 +6855,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46266</v>
+        <v>45761</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6865,13 +6870,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6914,7 +6914,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6924,14 +6924,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45319</v>
+        <v>45386</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6997,14 +6997,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45541</v>
+        <v>45319</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7060,7 +7060,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46230</v>
+        <v>45293</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7133,7 +7133,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7143,14 +7143,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45386</v>
+        <v>45789</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7206,7 +7206,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7220,10 +7220,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44899</v>
+        <v>45635</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7279,7 +7279,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45293</v>
+        <v>45173</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7352,7 +7352,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7362,14 +7362,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45789</v>
+        <v>45051</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
         <v>45278</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7512,10 +7512,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45635</v>
+        <v>45436</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
         <v>45006</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60261-2024</t>
+          <t>A 53422-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45642</v>
+        <v>45229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -861,151 +861,151 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 60261-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45642</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 53422-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5311-2022</t>
+          <t>A 61174-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44594</v>
+        <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1044,13 +1044,13 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1062,156 +1062,156 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Nordbjörnbär</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 61174-2025 artfynd.xlsx", "A 61174-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 61174-2025 karta.png", "A 61174-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 61174-2025 georefererad karta.tif", "A 61174-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 61174-2025 FSC-klagomål.docx", "A 61174-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 61174-2025 FSC-klagomål mail.docx", "A 61174-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 61174-2025 tillsynsbegäran.docx", "A 61174-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 61174-2025 tillsynsbegäran mail.docx", "A 61174-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 5311-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44594</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
         <v>3</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>3</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 5311-2022 artfynd.xlsx", "A 5311-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 5311-2022 karta.png", "A 5311-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 5311-2022 georefererad karta.tif", "A 5311-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 5311-2022 FSC-klagomål.docx", "A 5311-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 5311-2022 FSC-klagomål mail.docx", "A 5311-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 5311-2022 tillsynsbegäran.docx", "A 5311-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 5311-2022 tillsynsbegäran mail.docx", "A 5311-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 61174-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46000</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Nordbjörnbär</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 61174-2025 artfynd.xlsx", "A 61174-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 61174-2025 karta.png", "A 61174-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 61174-2025 georefererad karta.tif", "A 61174-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 61174-2025 FSC-klagomål.docx", "A 61174-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 61174-2025 FSC-klagomål mail.docx", "A 61174-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 61174-2025 tillsynsbegäran.docx", "A 61174-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 61174-2025 tillsynsbegäran mail.docx", "A 61174-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44475</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44746</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>44472</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45366</v>
+        <v>44903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45386</v>
+        <v>44977</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45590</v>
+        <v>45016</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46070</v>
+        <v>44903</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45155</v>
+        <v>44903</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2018,7 +2018,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46076</v>
+        <v>45188</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2101,14 +2101,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46076</v>
+        <v>45155</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46086</v>
+        <v>45590</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46086</v>
+        <v>45386</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45016</v>
+        <v>45574</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46090</v>
+        <v>44977</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46090</v>
+        <v>45894</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2539,14 +2539,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45182</v>
+        <v>45901</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 41381-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46099</v>
+        <v>45898</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45852</v>
+        <v>45155</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45852</v>
+        <v>45905</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.1</v>
+        <v>2.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45859</v>
+        <v>45910</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46111</v>
+        <v>45915</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46112</v>
+        <v>45761</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45894</v>
+        <v>45761</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 38036-2025</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45881</v>
+        <v>45761</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44977</v>
+        <v>44497</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 41381-2025</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45898</v>
+        <v>45642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46128</v>
+        <v>45229</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45901</v>
+        <v>45642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3478,7 +3478,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46133</v>
+        <v>45642</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45905</v>
+        <v>45933</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3624,7 +3624,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45910</v>
+        <v>45847</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45915</v>
+        <v>45436</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3770,7 +3770,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45642</v>
+        <v>45965</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44903</v>
+        <v>46155</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>10.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45642</v>
+        <v>46154</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46154</v>
+        <v>44929</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46154</v>
+        <v>45980</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45229</v>
+        <v>46154</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45933</v>
+        <v>45980</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45642</v>
+        <v>45164</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46155</v>
+        <v>45653</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>10.4</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45847</v>
+        <v>46042</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4500,7 +4500,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 25009-2023</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45085</v>
+        <v>45436</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4573,7 +4573,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45574</v>
+        <v>45673</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45541</v>
+        <v>46059</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45965</v>
+        <v>46059</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46243</v>
+        <v>46064</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45653</v>
+        <v>44977</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45980</v>
+        <v>46070</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5021,14 +5021,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45980</v>
+        <v>46076</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45155</v>
+        <v>46076</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45188</v>
+        <v>46086</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44903</v>
+        <v>46086</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44903</v>
+        <v>46090</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46261</v>
+        <v>46090</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 25009-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46157</v>
+        <v>45085</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46266</v>
+        <v>46099</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5551,13 +5551,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5600,7 +5595,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5614,10 +5609,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46230</v>
+        <v>46112</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5630,7 +5625,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5673,7 +5668,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5687,10 +5682,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45436</v>
+        <v>46111</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5703,7 +5698,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5746,7 +5741,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5760,10 +5755,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44899</v>
+        <v>46243</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5776,7 +5771,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5819,7 +5814,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5833,10 +5828,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44977</v>
+        <v>46128</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5849,7 +5844,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5892,7 +5887,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5902,14 +5897,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44497</v>
+        <v>45182</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5922,7 +5917,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5965,7 +5960,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5979,10 +5974,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46042</v>
+        <v>46133</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5995,7 +5990,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6038,7 +6033,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6052,10 +6047,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45436</v>
+        <v>45386</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6068,7 +6063,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6111,7 +6106,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6125,10 +6120,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45673</v>
+        <v>45366</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6141,7 +6136,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6184,7 +6179,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6194,14 +6189,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45386</v>
+        <v>45319</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6214,7 +6209,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6257,7 +6252,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6271,10 +6266,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45164</v>
+        <v>45541</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6287,7 +6282,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6330,7 +6325,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6344,10 +6339,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46059</v>
+        <v>46157</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6360,7 +6355,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6403,7 +6398,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6417,10 +6412,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46059</v>
+        <v>46261</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6433,7 +6428,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6476,7 +6471,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6490,10 +6485,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46064</v>
+        <v>45386</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6506,7 +6501,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6549,7 +6544,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6563,10 +6558,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44929</v>
+        <v>46266</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6578,8 +6573,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6622,7 +6622,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6636,10 +6636,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44977</v>
+        <v>44899</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6695,7 +6695,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45761</v>
+        <v>46230</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6768,7 +6768,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6782,10 +6782,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45761</v>
+        <v>45293</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6841,7 +6841,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6851,14 +6851,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45761</v>
+        <v>45789</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6914,7 +6914,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45386</v>
+        <v>45278</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6997,14 +6997,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45319</v>
+        <v>45635</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7060,7 +7060,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45293</v>
+        <v>45051</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7133,7 +7133,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7143,14 +7143,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45789</v>
+        <v>45173</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7206,7 +7206,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7220,10 +7220,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45635</v>
+        <v>45436</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7279,7 +7279,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45173</v>
+        <v>45852</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7352,7 +7352,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45051</v>
+        <v>45852</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7425,7 +7425,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7439,10 +7439,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45278</v>
+        <v>45859</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7498,7 +7498,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 38036-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7512,10 +7512,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45436</v>
+        <v>45881</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
         <v>45006</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>45229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>45642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44475</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44746</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>44472</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>44903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>44977</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>45016</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44903</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>44903</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>45188</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45155</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>45590</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45386</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>45574</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>44977</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>45894</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>45901</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>45898</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45155</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>45905</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>45910</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>45915</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>45761</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>45761</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>45761</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44497</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>45642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>45229</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>45642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>45642</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>45933</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>45847</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>45436</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45965</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>46155</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>46154</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>44929</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>45980</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>46154</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>45980</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>45164</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>45653</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>46042</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>45436</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>45673</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>46059</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>46059</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>46064</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>44977</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>46070</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>46076</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>46076</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>46086</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>46086</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>46090</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>46090</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45085</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>46099</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>46112</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>46111</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>46243</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>46128</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>45182</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>46133</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>45386</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>45366</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>45319</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>45541</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>46157</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>46261</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45386</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>46266</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44899</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>46230</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>45293</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>45789</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>45278</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45635</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45051</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>45173</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45436</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45852</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>45852</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>45859</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>45881</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>45006</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE95"/>
+  <dimension ref="A1:AE94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>45229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>45642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 61174-2025</t>
+          <t>A 5311-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46000</v>
+        <v>44594</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1044,13 +1044,13 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1062,156 +1062,156 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 5311-2022 artfynd.xlsx", "A 5311-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 5311-2022 karta.png", "A 5311-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 5311-2022 georefererad karta.tif", "A 5311-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 5311-2022 FSC-klagomål.docx", "A 5311-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 5311-2022 FSC-klagomål mail.docx", "A 5311-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 5311-2022 tillsynsbegäran.docx", "A 5311-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 5311-2022 tillsynsbegäran mail.docx", "A 5311-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 61174-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46000</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Nordbjörnbär</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 61174-2025 artfynd.xlsx", "A 61174-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 61174-2025 karta.png", "A 61174-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 61174-2025 georefererad karta.tif", "A 61174-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 61174-2025 FSC-klagomål.docx", "A 61174-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 61174-2025 FSC-klagomål mail.docx", "A 61174-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 61174-2025 tillsynsbegäran.docx", "A 61174-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 61174-2025 tillsynsbegäran mail.docx", "A 61174-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 5311-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44594</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 5311-2022 artfynd.xlsx", "A 5311-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 5311-2022 karta.png", "A 5311-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 5311-2022 georefererad karta.tif", "A 5311-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 5311-2022 FSC-klagomål.docx", "A 5311-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 5311-2022 FSC-klagomål mail.docx", "A 5311-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 5311-2022 tillsynsbegäran.docx", "A 5311-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 5311-2022 tillsynsbegäran mail.docx", "A 5311-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44475</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44746</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>44472</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>44903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>44977</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>45016</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44903</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>44903</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>45188</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45155</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 38036-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45590</v>
+        <v>45881</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45386</v>
+        <v>45590</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45574</v>
+        <v>45386</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44977</v>
+        <v>45894</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45894</v>
+        <v>45901</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 41381-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45901</v>
+        <v>45898</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 41381-2025</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45898</v>
+        <v>45905</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45155</v>
+        <v>45910</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45905</v>
+        <v>45915</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45910</v>
+        <v>45574</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45915</v>
+        <v>44977</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45761</v>
+        <v>45642</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45761</v>
+        <v>45229</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45761</v>
+        <v>45642</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44497</v>
+        <v>45642</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45642</v>
+        <v>45933</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45229</v>
+        <v>45155</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45642</v>
+        <v>46155</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>10.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3478,7 +3478,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45642</v>
+        <v>46154</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45933</v>
+        <v>45847</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3624,7 +3624,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45847</v>
+        <v>46154</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45436</v>
+        <v>45761</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3770,7 +3770,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45965</v>
+        <v>45761</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46155</v>
+        <v>45761</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>10.4</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46154</v>
+        <v>45965</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44929</v>
+        <v>44497</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
         <v>45980</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46154</v>
+        <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45980</v>
+        <v>45436</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45164</v>
+        <v>44929</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45653</v>
+        <v>46042</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46042</v>
+        <v>45164</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4500,7 +4500,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45436</v>
+        <v>45673</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4573,7 +4573,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45673</v>
+        <v>46059</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4663,7 +4663,7 @@
         <v>46059</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46059</v>
+        <v>46064</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46064</v>
+        <v>46070</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4875,14 +4875,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44977</v>
+        <v>46076</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5021,14 +5021,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46076</v>
+        <v>45653</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5174,7 +5174,7 @@
         <v>46086</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>9.199999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5320,7 +5320,7 @@
         <v>46090</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46090</v>
+        <v>46099</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 25009-2023</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45085</v>
+        <v>45436</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46099</v>
+        <v>46112</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5609,10 +5609,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46111</v>
+        <v>46128</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46243</v>
+        <v>44977</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5814,7 +5814,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46128</v>
+        <v>46133</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5887,7 +5887,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5897,14 +5897,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45182</v>
+        <v>46157</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46133</v>
+        <v>46261</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6033,7 +6033,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6047,10 +6047,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45386</v>
+        <v>46266</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6062,8 +6062,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6106,7 +6111,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6116,14 +6121,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45366</v>
+        <v>45182</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6136,7 +6141,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6179,7 +6184,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6189,14 +6194,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45319</v>
+        <v>45386</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6209,7 +6214,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6252,7 +6257,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6266,10 +6271,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45541</v>
+        <v>46230</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6282,7 +6287,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6325,7 +6330,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6339,10 +6344,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46157</v>
+        <v>45366</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6355,7 +6360,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6398,7 +6403,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6408,14 +6413,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46261</v>
+        <v>45319</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6428,7 +6433,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6471,7 +6476,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6485,10 +6490,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45386</v>
+        <v>45541</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6501,7 +6506,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6544,7 +6549,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6558,10 +6563,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46266</v>
+        <v>46243</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6573,13 +6578,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6622,7 +6622,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6636,10 +6636,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44899</v>
+        <v>45386</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6695,7 +6695,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46230</v>
+        <v>44899</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6785,7 +6785,7 @@
         <v>45293</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>45789</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>45278</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45635</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45051</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>45173</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45436</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45852</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>45852</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>45859</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7495,27 +7495,27 @@
       </c>
       <c r="V93" s="2" t="inlineStr"/>
     </row>
-    <row r="94" ht="15" customHeight="1">
+    <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 38036-2025</t>
+          <t>S 986-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45881</v>
+        <v>45006</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7527,8 +7527,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7567,84 +7572,6 @@
         <v>0</v>
       </c>
       <c r="V94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>S 986-2023</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="n">
-        <v>45006</v>
-      </c>
-      <c r="E95" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I95" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J95" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
-      <c r="R95" t="n">
-        <v>0</v>
-      </c>
-      <c r="S95" t="n">
-        <v>0</v>
-      </c>
-      <c r="T95" t="n">
-        <v>0</v>
-      </c>
-      <c r="U95" t="n">
-        <v>0</v>
-      </c>
-      <c r="V95" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 53422-2023</t>
+          <t>A 60261-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45229</v>
+        <v>45642</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -861,151 +861,151 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 53422-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 60261-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45642</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5311-2022</t>
+          <t>A 61174-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44594</v>
+        <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1044,13 +1044,13 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1062,156 +1062,156 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Nordbjörnbär</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 61174-2025 artfynd.xlsx", "A 61174-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 61174-2025 karta.png", "A 61174-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 61174-2025 georefererad karta.tif", "A 61174-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 61174-2025 FSC-klagomål.docx", "A 61174-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 61174-2025 FSC-klagomål mail.docx", "A 61174-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 61174-2025 tillsynsbegäran.docx", "A 61174-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 61174-2025 tillsynsbegäran mail.docx", "A 61174-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 5311-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44594</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
         <v>3</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>3</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 5311-2022 artfynd.xlsx", "A 5311-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 5311-2022 karta.png", "A 5311-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 5311-2022 georefererad karta.tif", "A 5311-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 5311-2022 FSC-klagomål.docx", "A 5311-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 5311-2022 FSC-klagomål mail.docx", "A 5311-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 5311-2022 tillsynsbegäran.docx", "A 5311-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 5311-2022 tillsynsbegäran mail.docx", "A 5311-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 61174-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46000</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Nordbjörnbär</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 61174-2025 artfynd.xlsx", "A 61174-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 61174-2025 karta.png", "A 61174-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 61174-2025 georefererad karta.tif", "A 61174-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 61174-2025 FSC-klagomål.docx", "A 61174-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 61174-2025 FSC-klagomål mail.docx", "A 61174-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 61174-2025 tillsynsbegäran.docx", "A 61174-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 61174-2025 tillsynsbegäran mail.docx", "A 61174-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44475</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44746</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>44472</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1663,14 +1663,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44903</v>
+        <v>45789</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44977</v>
+        <v>45635</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45016</v>
+        <v>45173</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44903</v>
+        <v>45051</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44903</v>
+        <v>45366</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2018,7 +2018,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45188</v>
+        <v>45278</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45155</v>
+        <v>44903</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38036-2025</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45881</v>
+        <v>45386</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45590</v>
+        <v>45894</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 41381-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45386</v>
+        <v>45898</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45894</v>
+        <v>45901</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45901</v>
+        <v>45905</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41381-2025</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45898</v>
+        <v>45910</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45905</v>
+        <v>45915</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45910</v>
+        <v>45590</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45915</v>
+        <v>45642</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45574</v>
+        <v>45642</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44977</v>
+        <v>45229</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45642</v>
+        <v>45933</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45229</v>
+        <v>45642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45642</v>
+        <v>45847</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45642</v>
+        <v>45574</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45933</v>
+        <v>45436</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3349,7 +3349,7 @@
         <v>45155</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46155</v>
+        <v>45541</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>10.4</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3478,7 +3478,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46154</v>
+        <v>45016</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45847</v>
+        <v>45182</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3624,7 +3624,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46154</v>
+        <v>45965</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45761</v>
+        <v>45653</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3770,7 +3770,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45761</v>
+        <v>45980</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45761</v>
+        <v>45980</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45965</v>
+        <v>45155</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44497</v>
+        <v>45188</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45980</v>
+        <v>44977</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45980</v>
+        <v>44903</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45436</v>
+        <v>44903</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44929</v>
+        <v>46042</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46042</v>
+        <v>45673</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45164</v>
+        <v>46243</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4500,7 +4500,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45673</v>
+        <v>46059</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4590,7 +4590,7 @@
         <v>46059</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46059</v>
+        <v>46064</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46064</v>
+        <v>45436</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
         <v>46070</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4875,14 +4875,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
         <v>46076</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4948,14 +4948,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
         <v>46076</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45653</v>
+        <v>44899</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
         <v>46086</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>46086</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46090</v>
+        <v>44977</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46090</v>
+        <v>44497</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46099</v>
+        <v>46090</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45436</v>
+        <v>46090</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46112</v>
+        <v>46099</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5609,10 +5609,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46111</v>
+        <v>45852</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46128</v>
+        <v>45852</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44977</v>
+        <v>45859</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5814,7 +5814,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46133</v>
+        <v>46111</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5887,7 +5887,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46157</v>
+        <v>45436</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46261</v>
+        <v>46112</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6033,7 +6033,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6047,10 +6047,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46266</v>
+        <v>45386</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6062,13 +6062,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6111,7 +6106,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6121,14 +6116,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45182</v>
+        <v>45164</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6184,7 +6179,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6198,10 +6193,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45386</v>
+        <v>46128</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6214,7 +6209,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6257,7 +6252,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6271,10 +6266,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46230</v>
+        <v>46133</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6287,7 +6282,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6330,7 +6325,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6344,10 +6339,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45366</v>
+        <v>44929</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6360,7 +6355,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6403,7 +6398,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6413,14 +6408,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45319</v>
+        <v>44977</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6433,7 +6428,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6476,7 +6471,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6490,10 +6485,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45541</v>
+        <v>45761</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6506,7 +6501,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6549,7 +6544,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6563,10 +6558,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46243</v>
+        <v>45761</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6579,7 +6574,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6622,7 +6617,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6636,10 +6631,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45386</v>
+        <v>45761</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6652,7 +6647,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6695,7 +6690,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 38036-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6709,10 +6704,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44899</v>
+        <v>45881</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6725,7 +6720,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6768,7 +6763,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6782,10 +6777,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45293</v>
+        <v>45386</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6798,7 +6793,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6841,7 +6836,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6855,10 +6850,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45789</v>
+        <v>45319</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6871,7 +6866,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6914,7 +6909,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6928,10 +6923,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45278</v>
+        <v>46154</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6944,7 +6939,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6987,7 +6982,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7001,10 +6996,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45635</v>
+        <v>45293</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7017,7 +7012,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7060,7 +7055,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7074,10 +7069,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45051</v>
+        <v>46154</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7090,7 +7085,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7133,7 +7128,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7147,10 +7142,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45173</v>
+        <v>46155</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7163,7 +7158,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.3</v>
+        <v>10.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7206,7 +7201,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7220,10 +7215,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45436</v>
+        <v>46261</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7236,7 +7231,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7279,7 +7274,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7293,10 +7288,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45852</v>
+        <v>46157</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7309,7 +7304,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7352,7 +7347,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7366,10 +7361,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45852</v>
+        <v>46266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7381,8 +7376,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7425,7 +7425,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7439,10 +7439,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45859</v>
+        <v>46230</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>45006</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60261-2024</t>
+          <t>A 53422-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45642</v>
+        <v>45229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -861,147 +861,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 60261-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45642</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 53422-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44475</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44746</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>44472</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1663,14 +1663,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45789</v>
+        <v>44903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45635</v>
+        <v>44977</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45173</v>
+        <v>45016</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45051</v>
+        <v>44903</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45366</v>
+        <v>44903</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2018,7 +2018,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45278</v>
+        <v>45188</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44903</v>
+        <v>45155</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45386</v>
+        <v>45590</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 38036-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45894</v>
+        <v>45881</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41381-2025</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45898</v>
+        <v>45386</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45901</v>
+        <v>45894</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45905</v>
+        <v>45901</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 41381-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45910</v>
+        <v>45898</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45915</v>
+        <v>45905</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45590</v>
+        <v>45910</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45642</v>
+        <v>45915</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45642</v>
+        <v>45574</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45229</v>
+        <v>44977</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45933</v>
+        <v>45642</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45642</v>
+        <v>45229</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45847</v>
+        <v>45155</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45574</v>
+        <v>45642</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45436</v>
+        <v>45642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45155</v>
+        <v>45933</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45541</v>
+        <v>45847</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3478,7 +3478,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45016</v>
+        <v>45761</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45182</v>
+        <v>45761</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3624,7 +3624,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45965</v>
+        <v>45761</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45653</v>
+        <v>44497</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3770,7 +3770,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45980</v>
+        <v>45965</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45980</v>
+        <v>45436</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45155</v>
+        <v>45980</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45188</v>
+        <v>45980</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44977</v>
+        <v>46155</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>10.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44903</v>
+        <v>46154</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44903</v>
+        <v>46154</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46042</v>
+        <v>44929</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45673</v>
+        <v>45164</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46243</v>
+        <v>46042</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46059</v>
+        <v>45673</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4590,7 +4590,7 @@
         <v>46059</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46064</v>
+        <v>46059</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45436</v>
+        <v>46064</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46070</v>
+        <v>45653</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46076</v>
+        <v>46070</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
         <v>46076</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44899</v>
+        <v>46076</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
         <v>46086</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>46086</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44977</v>
+        <v>46090</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44497</v>
+        <v>46090</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46090</v>
+        <v>45436</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46090</v>
+        <v>46099</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46099</v>
+        <v>46112</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5609,10 +5609,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45852</v>
+        <v>46111</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45852</v>
+        <v>44977</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45859</v>
+        <v>46128</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5814,7 +5814,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46111</v>
+        <v>46133</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5887,7 +5887,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5897,14 +5897,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45436</v>
+        <v>45182</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46112</v>
+        <v>45386</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6033,7 +6033,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6047,10 +6047,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45386</v>
+        <v>46157</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6106,7 +6106,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45164</v>
+        <v>46261</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6179,7 +6179,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46128</v>
+        <v>46266</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6206,6 +6206,11 @@
       <c r="G76" t="inlineStr">
         <is>
           <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -6252,7 +6257,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6266,10 +6271,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46133</v>
+        <v>45366</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6282,7 +6287,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6325,7 +6330,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6339,10 +6344,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44929</v>
+        <v>46230</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6355,7 +6360,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6398,7 +6403,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6408,14 +6413,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44977</v>
+        <v>45319</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6428,7 +6433,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6471,7 +6476,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6485,10 +6490,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45761</v>
+        <v>45541</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6501,7 +6506,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6544,7 +6549,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6558,10 +6563,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45761</v>
+        <v>45386</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6574,7 +6579,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6617,7 +6622,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6631,10 +6636,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45761</v>
+        <v>44899</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6647,7 +6652,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6690,7 +6695,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 38036-2025</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6704,10 +6709,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45881</v>
+        <v>46243</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6720,7 +6725,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6763,7 +6768,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6777,10 +6782,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45386</v>
+        <v>45293</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6793,7 +6798,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6836,7 +6841,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6850,10 +6855,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45319</v>
+        <v>45789</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6866,7 +6871,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6909,7 +6914,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6923,10 +6928,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46154</v>
+        <v>45278</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6939,7 +6944,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6982,7 +6987,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6996,10 +7001,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45293</v>
+        <v>45635</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7012,7 +7017,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7055,7 +7060,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7069,10 +7074,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46154</v>
+        <v>45051</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7085,7 +7090,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7128,7 +7133,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7142,10 +7147,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46155</v>
+        <v>45173</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7158,7 +7163,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>10.4</v>
+        <v>2.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7201,7 +7206,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7215,10 +7220,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46261</v>
+        <v>45436</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7231,7 +7236,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7274,7 +7279,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7288,10 +7293,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46157</v>
+        <v>45852</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7304,7 +7309,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7347,7 +7352,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7361,10 +7366,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46266</v>
+        <v>45852</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7376,13 +7381,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7425,7 +7425,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7439,10 +7439,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46230</v>
+        <v>45859</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>45006</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 53422-2023</t>
+          <t>A 60261-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45229</v>
+        <v>45642</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -861,147 +861,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 53422-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 60261-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45642</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44475</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44746</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>44472</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44903</v>
+        <v>45366</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44977</v>
+        <v>45386</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45016</v>
+        <v>45635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44903</v>
+        <v>45173</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44903</v>
+        <v>45051</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2018,7 +2018,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45188</v>
+        <v>45278</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45155</v>
+        <v>45894</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45590</v>
+        <v>46042</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38036-2025</t>
+          <t>A 41381-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45881</v>
+        <v>45898</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45386</v>
+        <v>45901</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45894</v>
+        <v>45673</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45901</v>
+        <v>45590</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41381-2025</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45898</v>
+        <v>45905</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45905</v>
+        <v>45910</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45910</v>
+        <v>45915</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45915</v>
+        <v>46059</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45574</v>
+        <v>46059</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44977</v>
+        <v>46064</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45642</v>
+        <v>46070</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45229</v>
+        <v>46076</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3123,14 +3123,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45155</v>
+        <v>46076</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45642</v>
+        <v>45155</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45642</v>
+        <v>46086</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45933</v>
+        <v>45642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45847</v>
+        <v>45642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3478,7 +3478,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45761</v>
+        <v>46086</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45761</v>
+        <v>45229</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3624,7 +3624,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45761</v>
+        <v>45933</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44497</v>
+        <v>45642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3770,7 +3770,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45965</v>
+        <v>46090</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45436</v>
+        <v>46090</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45980</v>
+        <v>45847</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45980</v>
+        <v>46099</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46155</v>
+        <v>45016</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>10.4</v>
+        <v>1.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4145,14 +4145,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46154</v>
+        <v>45182</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46154</v>
+        <v>46111</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44929</v>
+        <v>46112</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45164</v>
+        <v>45965</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46042</v>
+        <v>45436</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45673</v>
+        <v>46128</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4573,7 +4573,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46059</v>
+        <v>45980</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46059</v>
+        <v>45980</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46064</v>
+        <v>46133</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45653</v>
+        <v>44977</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46070</v>
+        <v>46154</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4948,14 +4948,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46076</v>
+        <v>46154</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46076</v>
+        <v>46155</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>10.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46086</v>
+        <v>44903</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46086</v>
+        <v>45852</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>9.199999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46090</v>
+        <v>45852</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46090</v>
+        <v>45859</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45436</v>
+        <v>45574</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46099</v>
+        <v>45541</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 38036-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46112</v>
+        <v>45881</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5609,10 +5609,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46111</v>
+        <v>45653</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44977</v>
+        <v>46261</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46128</v>
+        <v>46157</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5814,7 +5814,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46133</v>
+        <v>45155</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5887,7 +5887,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5897,14 +5897,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45182</v>
+        <v>45188</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45386</v>
+        <v>46266</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5989,8 +5989,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6033,7 +6038,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6047,10 +6052,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46157</v>
+        <v>44903</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6063,7 +6068,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6106,7 +6111,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6120,10 +6125,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46261</v>
+        <v>44903</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6136,7 +6141,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6179,7 +6184,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6193,10 +6198,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46266</v>
+        <v>46230</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6208,13 +6213,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6257,7 +6257,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6271,10 +6271,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45366</v>
+        <v>45436</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6330,7 +6330,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46230</v>
+        <v>46243</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6403,7 +6403,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6413,14 +6413,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45319</v>
+        <v>44899</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6476,7 +6476,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6490,10 +6490,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45541</v>
+        <v>44977</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6549,7 +6549,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45386</v>
+        <v>44497</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6622,7 +6622,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6636,10 +6636,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44899</v>
+        <v>45436</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6695,7 +6695,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46243</v>
+        <v>45386</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6768,7 +6768,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6782,10 +6782,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45293</v>
+        <v>45164</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6841,7 +6841,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6851,14 +6851,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45789</v>
+        <v>44929</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6914,7 +6914,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45278</v>
+        <v>44977</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45635</v>
+        <v>45761</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7060,7 +7060,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45051</v>
+        <v>45761</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7133,7 +7133,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45173</v>
+        <v>45761</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7206,7 +7206,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7220,10 +7220,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45436</v>
+        <v>45386</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7279,7 +7279,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7289,14 +7289,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45852</v>
+        <v>45319</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7352,7 +7352,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45852</v>
+        <v>45293</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7425,7 +7425,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7435,14 +7435,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45859</v>
+        <v>45789</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>45006</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>45642</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>45229</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44475</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44746</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>44472</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>45366</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>45386</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>45635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>45173</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>45051</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>45278</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45894</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>46042</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45898</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>45901</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>45673</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>45590</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>45905</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>45910</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45915</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>46059</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>46059</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>46064</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>46070</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>46076</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>46076</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45155</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>46086</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>45642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>45642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>46086</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>45229</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>45933</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>45642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>46090</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>46090</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>45847</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>46099</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>45016</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45182</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>46111</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>46112</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>45965</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>45436</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>46128</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>45980</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>45980</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>46133</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>44977</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>46154</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>46154</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>46155</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>44903</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>45852</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>45852</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>45859</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>45574</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45541</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>45881</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>45653</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>46261</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>46157</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45155</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>45188</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>46266</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>44903</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>44903</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>46230</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>45436</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>46243</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>44899</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>44977</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>44497</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>45436</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>45386</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>45164</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>44929</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>44977</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45761</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45761</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>45761</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45386</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45319</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>45293</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>45789</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>45006</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>45642</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>45229</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44475</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44746</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>44472</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>45366</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>45386</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>45635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>45173</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>45051</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>45278</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45894</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>46042</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45898</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>45901</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>45673</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>45590</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>45905</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>45910</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45915</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>46059</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>46059</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>46064</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>46070</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>46076</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>46076</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45155</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>46086</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>45642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>45642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>46086</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>45229</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>45933</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>45642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>46090</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>46090</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>45847</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>46099</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>45016</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45182</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>46111</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>46112</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>45965</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>45436</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>46128</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>45980</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>45980</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>46133</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>44977</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>46154</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>46154</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>46155</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>44903</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>45852</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>45852</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>45859</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>45574</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45541</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>45881</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>45653</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>46261</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>46157</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45155</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>45188</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>46266</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>44903</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>44903</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>46230</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>45436</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>46243</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>44899</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>44977</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>44497</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>45436</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>45386</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>45164</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>44929</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>44977</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45761</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45761</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>45761</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45386</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45319</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>45293</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>45789</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>45006</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60261-2024</t>
+          <t>A 53422-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45642</v>
+        <v>45229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -861,147 +861,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 60261-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45642</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 53422-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44475</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44746</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>44472</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45366</v>
+        <v>44903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45386</v>
+        <v>44977</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45635</v>
+        <v>45293</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1882,14 +1882,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45173</v>
+        <v>45789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45051</v>
+        <v>45278</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2018,7 +2018,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45278</v>
+        <v>45635</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45894</v>
+        <v>45051</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46042</v>
+        <v>45016</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41381-2025</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45898</v>
+        <v>45173</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45901</v>
+        <v>45894</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45673</v>
+        <v>45901</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 41381-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45590</v>
+        <v>45898</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2546,7 +2546,7 @@
         <v>45905</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>45910</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45915</v>
+        <v>45436</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46059</v>
+        <v>45915</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46059</v>
+        <v>44903</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46064</v>
+        <v>44903</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46070</v>
+        <v>45642</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46076</v>
+        <v>45229</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3123,14 +3123,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46076</v>
+        <v>45642</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45155</v>
+        <v>45642</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46086</v>
+        <v>45933</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45642</v>
+        <v>45847</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45642</v>
+        <v>45188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3478,7 +3478,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46086</v>
+        <v>45852</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>9.199999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45229</v>
+        <v>45852</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3624,7 +3624,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45933</v>
+        <v>45859</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45642</v>
+        <v>45965</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3770,7 +3770,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 38036-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46090</v>
+        <v>45881</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46090</v>
+        <v>46042</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45847</v>
+        <v>45980</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46099</v>
+        <v>45155</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45016</v>
+        <v>45980</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4145,14 +4145,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45182</v>
+        <v>45590</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46111</v>
+        <v>45673</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46112</v>
+        <v>45386</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45965</v>
+        <v>46059</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45436</v>
+        <v>46059</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4500,7 +4500,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46128</v>
+        <v>46064</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4573,7 +4573,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45980</v>
+        <v>46070</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45980</v>
+        <v>45574</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4729,14 +4729,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46133</v>
+        <v>46076</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44977</v>
+        <v>46076</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46154</v>
+        <v>44977</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46154</v>
+        <v>46086</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46155</v>
+        <v>46086</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>10.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44903</v>
+        <v>45155</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45852</v>
+        <v>46090</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45852</v>
+        <v>46090</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45859</v>
+        <v>46099</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45574</v>
+        <v>45761</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45541</v>
+        <v>45761</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 38036-2025</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45881</v>
+        <v>45761</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5609,10 +5609,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45653</v>
+        <v>44497</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46261</v>
+        <v>46112</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46157</v>
+        <v>46111</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5814,7 +5814,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45155</v>
+        <v>45436</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5887,7 +5887,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45188</v>
+        <v>46128</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46266</v>
+        <v>46133</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5989,13 +5989,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6038,7 +6033,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6052,10 +6047,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44903</v>
+        <v>44929</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6068,7 +6063,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6111,7 +6106,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6125,10 +6120,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44903</v>
+        <v>45164</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6184,7 +6179,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6198,10 +6193,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46230</v>
+        <v>46155</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6214,7 +6209,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.3</v>
+        <v>10.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6257,7 +6252,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6271,10 +6266,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45436</v>
+        <v>46154</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6287,7 +6282,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6330,7 +6325,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6344,10 +6339,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46243</v>
+        <v>46154</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6360,7 +6355,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6403,7 +6398,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6417,10 +6412,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44899</v>
+        <v>45653</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6433,7 +6428,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6476,7 +6471,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6490,10 +6485,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44977</v>
+        <v>45436</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6506,7 +6501,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6549,7 +6544,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6563,10 +6558,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44497</v>
+        <v>44977</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6579,7 +6574,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6622,7 +6617,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6632,14 +6627,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45436</v>
+        <v>45182</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6652,7 +6647,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6712,7 +6707,7 @@
         <v>45386</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6768,7 +6763,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6782,10 +6777,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45164</v>
+        <v>46157</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6798,7 +6793,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6841,7 +6836,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6855,10 +6850,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44929</v>
+        <v>46261</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6871,7 +6866,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6914,7 +6909,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6928,10 +6923,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44977</v>
+        <v>45366</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6944,7 +6939,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6987,7 +6982,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7001,10 +6996,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45761</v>
+        <v>46266</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7016,8 +7011,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7060,7 +7060,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7070,14 +7070,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45761</v>
+        <v>45319</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7133,7 +7133,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45761</v>
+        <v>45541</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7206,7 +7206,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7220,10 +7220,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45386</v>
+        <v>46230</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7279,7 +7279,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7289,14 +7289,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45319</v>
+        <v>45386</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7352,7 +7352,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45293</v>
+        <v>44899</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7425,7 +7425,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7435,14 +7435,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45789</v>
+        <v>46243</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>45006</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 53422-2023</t>
+          <t>A 60261-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45229</v>
+        <v>45642</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -861,147 +861,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 53422-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 60261-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45642</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44475</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44746</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>44472</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44903</v>
+        <v>45366</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44977</v>
+        <v>45386</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1809,14 +1809,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45293</v>
+        <v>45789</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1882,14 +1882,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45789</v>
+        <v>45635</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45278</v>
+        <v>45173</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2018,7 +2018,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45635</v>
+        <v>45051</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45051</v>
+        <v>45278</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45016</v>
+        <v>45894</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 41381-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45173</v>
+        <v>45898</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45894</v>
+        <v>45901</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45901</v>
+        <v>45905</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41381-2025</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45898</v>
+        <v>45590</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45905</v>
+        <v>45910</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45910</v>
+        <v>45436</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45436</v>
+        <v>45915</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45915</v>
+        <v>46042</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44903</v>
+        <v>45155</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44903</v>
+        <v>45642</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2984,7 +2984,7 @@
         <v>45642</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>45229</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45642</v>
+        <v>45933</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3203,7 +3203,7 @@
         <v>45642</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45933</v>
+        <v>45847</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45847</v>
+        <v>45852</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45188</v>
+        <v>45852</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3478,7 +3478,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45852</v>
+        <v>45859</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45852</v>
+        <v>45016</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3624,7 +3624,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45859</v>
+        <v>45673</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3707,14 +3707,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45965</v>
+        <v>45182</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
         <v>45881</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46042</v>
+        <v>46059</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45980</v>
+        <v>46059</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45155</v>
+        <v>45965</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45980</v>
+        <v>46064</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45590</v>
+        <v>46070</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45673</v>
+        <v>45980</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45386</v>
+        <v>45980</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>8</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46059</v>
+        <v>46076</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4437,14 +4437,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46059</v>
+        <v>46076</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4500,7 +4500,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46064</v>
+        <v>44977</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4573,7 +4573,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45574</v>
+        <v>46086</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4729,14 +4729,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46076</v>
+        <v>46090</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46076</v>
+        <v>46090</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44977</v>
+        <v>46099</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46086</v>
+        <v>46111</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46086</v>
+        <v>46112</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>9.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45155</v>
+        <v>46128</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46090</v>
+        <v>44903</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46090</v>
+        <v>46133</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46099</v>
+        <v>45574</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45761</v>
+        <v>45541</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45761</v>
+        <v>46154</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45761</v>
+        <v>46154</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5609,10 +5609,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44497</v>
+        <v>46155</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>10.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46112</v>
+        <v>45653</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46111</v>
+        <v>45155</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.3</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5814,7 +5814,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45436</v>
+        <v>45188</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5887,7 +5887,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46128</v>
+        <v>44903</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46133</v>
+        <v>44903</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6033,7 +6033,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6047,10 +6047,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44929</v>
+        <v>45436</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6106,7 +6106,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45164</v>
+        <v>44899</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6179,7 +6179,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46155</v>
+        <v>44977</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>10.4</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6252,7 +6252,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46154</v>
+        <v>44497</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6325,7 +6325,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46154</v>
+        <v>45436</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6398,7 +6398,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45653</v>
+        <v>46261</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6471,7 +6471,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45436</v>
+        <v>46157</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6544,7 +6544,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6558,10 +6558,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44977</v>
+        <v>45386</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6617,7 +6617,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6627,14 +6627,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45182</v>
+        <v>46266</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6646,8 +6646,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6690,7 +6695,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6704,10 +6709,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45386</v>
+        <v>45164</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6720,7 +6725,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6763,7 +6768,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6777,10 +6782,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46157</v>
+        <v>44929</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6793,7 +6798,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6836,7 +6841,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6850,10 +6855,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46261</v>
+        <v>44977</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6866,7 +6871,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.1</v>
+        <v>0.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6909,7 +6914,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6923,10 +6928,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45366</v>
+        <v>45761</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6939,7 +6944,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6982,7 +6987,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6996,10 +7001,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46266</v>
+        <v>45761</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7009,11 +7014,6 @@
       <c r="G87" t="inlineStr">
         <is>
           <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -7060,7 +7060,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7070,14 +7070,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45319</v>
+        <v>45761</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7133,7 +7133,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45541</v>
+        <v>46230</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7206,7 +7206,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7220,10 +7220,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46230</v>
+        <v>45386</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7279,7 +7279,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7289,14 +7289,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45386</v>
+        <v>45319</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7352,7 +7352,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44899</v>
+        <v>46243</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7425,7 +7425,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7439,10 +7439,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46243</v>
+        <v>45293</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>45006</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60261-2024</t>
+          <t>A 53422-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45642</v>
+        <v>45229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -861,147 +861,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 60261-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45642</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 53422-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44475</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28159-2022</t>
+          <t>A 54313-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1448,10 +1448,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44746</v>
+        <v>44472</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1507,7 +1507,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 54313-2021</t>
+          <t>A 60972-2021</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1517,14 +1517,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44472</v>
+        <v>44497</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1580,7 +1580,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 60972-2021</t>
+          <t>A 28159-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44497</v>
+        <v>44746</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45366</v>
+        <v>44903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45386</v>
+        <v>45155</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>0.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1809,14 +1809,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45789</v>
+        <v>45366</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45635</v>
+        <v>45653</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45173</v>
+        <v>45590</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2018,7 +2018,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2028,14 +2028,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45051</v>
+        <v>45319</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45278</v>
+        <v>45386</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45894</v>
+        <v>45541</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41381-2025</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45898</v>
+        <v>45436</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45901</v>
+        <v>45386</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45905</v>
+        <v>44977</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45590</v>
+        <v>45574</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45910</v>
+        <v>44977</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45436</v>
+        <v>44977</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45915</v>
+        <v>44899</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46042</v>
+        <v>45155</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45155</v>
+        <v>45293</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45642</v>
+        <v>45761</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45642</v>
+        <v>45761</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45229</v>
+        <v>45761</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45933</v>
+        <v>44497</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3196,14 +3196,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45642</v>
+        <v>45789</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45847</v>
+        <v>45016</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45852</v>
+        <v>45278</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45852</v>
+        <v>45635</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3478,7 +3478,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45859</v>
+        <v>45051</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45016</v>
+        <v>45173</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3624,7 +3624,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45673</v>
+        <v>44903</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3707,14 +3707,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45182</v>
+        <v>44903</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38036-2025</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45881</v>
+        <v>45436</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46059</v>
+        <v>45436</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3926,14 +3926,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46059</v>
+        <v>45182</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45965</v>
+        <v>45386</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46064</v>
+        <v>44929</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46070</v>
+        <v>45852</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.4</v>
+        <v>0.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45980</v>
+        <v>45852</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45980</v>
+        <v>45859</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46076</v>
+        <v>45188</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4437,14 +4437,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46076</v>
+        <v>45164</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4500,7 +4500,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44977</v>
+        <v>45933</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4573,7 +4573,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46086</v>
+        <v>45847</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 38036-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46086</v>
+        <v>45881</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>9.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46090</v>
+        <v>45894</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46090</v>
+        <v>45901</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 41381-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46099</v>
+        <v>45898</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46111</v>
+        <v>45905</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46112</v>
+        <v>45910</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46128</v>
+        <v>45965</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44903</v>
+        <v>45915</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46133</v>
+        <v>45642</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45574</v>
+        <v>45229</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45541</v>
+        <v>45980</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46154</v>
+        <v>45642</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46154</v>
+        <v>45642</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5609,10 +5609,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46155</v>
+        <v>45980</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>10.4</v>
+        <v>2.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45653</v>
+        <v>46042</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45155</v>
+        <v>45673</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5814,7 +5814,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45188</v>
+        <v>46059</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5887,7 +5887,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44903</v>
+        <v>46059</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44903</v>
+        <v>46064</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6033,7 +6033,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6047,10 +6047,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45436</v>
+        <v>46070</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6106,7 +6106,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6116,14 +6116,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44899</v>
+        <v>46076</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6179,7 +6179,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44977</v>
+        <v>46076</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6252,7 +6252,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44497</v>
+        <v>46086</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6325,7 +6325,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45436</v>
+        <v>46086</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6398,7 +6398,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46261</v>
+        <v>46090</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6471,7 +6471,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46157</v>
+        <v>46090</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6544,7 +6544,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6558,10 +6558,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45386</v>
+        <v>46099</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6617,7 +6617,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6631,10 +6631,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46266</v>
+        <v>46112</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6646,13 +6646,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6695,7 +6690,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6709,10 +6704,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45164</v>
+        <v>46111</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6725,7 +6720,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6768,7 +6763,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6782,10 +6777,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44929</v>
+        <v>46128</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6798,7 +6793,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6841,7 +6836,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6855,10 +6850,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44977</v>
+        <v>46133</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6871,7 +6866,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6914,7 +6909,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6928,10 +6923,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45761</v>
+        <v>46155</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6944,7 +6939,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>10.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6987,7 +6982,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7001,10 +6996,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45761</v>
+        <v>46154</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7017,7 +7012,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7060,7 +7055,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7074,10 +7069,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45761</v>
+        <v>46154</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7090,7 +7085,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7133,7 +7128,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7147,10 +7142,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46230</v>
+        <v>46157</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7163,7 +7158,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7206,7 +7201,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7220,10 +7215,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45386</v>
+        <v>46261</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7236,7 +7231,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7279,7 +7274,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7289,14 +7284,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45319</v>
+        <v>46266</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7308,8 +7303,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7352,7 +7352,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46243</v>
+        <v>46230</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7425,7 +7425,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7439,10 +7439,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45293</v>
+        <v>46243</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>45006</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 53422-2023</t>
+          <t>A 60261-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45229</v>
+        <v>45642</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -861,147 +861,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 53422-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 60261-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45642</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44475</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 54313-2021</t>
+          <t>A 28159-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1448,10 +1448,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44472</v>
+        <v>44746</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1507,7 +1507,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 60972-2021</t>
+          <t>A 54313-2021</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1517,14 +1517,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44497</v>
+        <v>44472</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1580,7 +1580,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 28159-2022</t>
+          <t>A 60972-2021</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44746</v>
+        <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44903</v>
+        <v>45366</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45155</v>
+        <v>45386</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1809,14 +1809,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45366</v>
+        <v>45789</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45653</v>
+        <v>45635</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45590</v>
+        <v>46042</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2018,7 +2018,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2028,14 +2028,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45319</v>
+        <v>45894</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45386</v>
+        <v>45173</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>2.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45541</v>
+        <v>45051</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45436</v>
+        <v>45673</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 41381-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45386</v>
+        <v>45898</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44977</v>
+        <v>45278</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45574</v>
+        <v>45901</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44977</v>
+        <v>45905</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44977</v>
+        <v>45910</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44899</v>
+        <v>46059</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45155</v>
+        <v>46059</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45293</v>
+        <v>46064</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45761</v>
+        <v>45915</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45761</v>
+        <v>45590</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45761</v>
+        <v>46070</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44497</v>
+        <v>46076</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45789</v>
+        <v>46076</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45016</v>
+        <v>45642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45278</v>
+        <v>45642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45635</v>
+        <v>45229</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3478,7 +3478,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45051</v>
+        <v>45933</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45173</v>
+        <v>45642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3624,7 +3624,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44903</v>
+        <v>46086</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44903</v>
+        <v>46086</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3770,7 +3770,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45436</v>
+        <v>45847</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45436</v>
+        <v>46090</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3926,14 +3926,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45182</v>
+        <v>46090</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45386</v>
+        <v>45155</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44929</v>
+        <v>46099</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45852</v>
+        <v>45016</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45852</v>
+        <v>46111</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4291,14 +4291,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45859</v>
+        <v>45182</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45188</v>
+        <v>46112</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45164</v>
+        <v>45965</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4500,7 +4500,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45933</v>
+        <v>45436</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4573,7 +4573,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45847</v>
+        <v>45980</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38036-2025</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45881</v>
+        <v>45980</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45894</v>
+        <v>46128</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45901</v>
+        <v>46133</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 41381-2025</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45898</v>
+        <v>44977</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45905</v>
+        <v>45852</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45910</v>
+        <v>45852</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>0.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45965</v>
+        <v>45859</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 38036-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45915</v>
+        <v>45881</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45642</v>
+        <v>46154</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45229</v>
+        <v>44903</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45980</v>
+        <v>46154</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45642</v>
+        <v>46155</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>10.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45642</v>
+        <v>45574</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5609,10 +5609,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45980</v>
+        <v>45541</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46042</v>
+        <v>45653</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45673</v>
+        <v>45155</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5814,7 +5814,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46059</v>
+        <v>45188</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5887,7 +5887,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46059</v>
+        <v>44903</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46064</v>
+        <v>44903</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6033,7 +6033,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6047,10 +6047,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46070</v>
+        <v>46261</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6106,7 +6106,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6116,14 +6116,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46076</v>
+        <v>46157</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6179,7 +6179,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46076</v>
+        <v>46266</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6208,8 +6208,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6252,7 +6257,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6266,10 +6271,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46086</v>
+        <v>46230</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6282,7 +6287,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6325,7 +6330,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6339,10 +6344,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46086</v>
+        <v>45436</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6355,7 +6360,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>9.199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6398,7 +6403,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6412,10 +6417,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46090</v>
+        <v>44899</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6428,7 +6433,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6471,7 +6476,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6485,10 +6490,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46090</v>
+        <v>44977</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6501,7 +6506,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6544,7 +6549,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6558,10 +6563,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46099</v>
+        <v>44497</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6574,7 +6579,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6617,7 +6622,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6631,10 +6636,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46112</v>
+        <v>46243</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6647,7 +6652,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6690,7 +6695,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6704,10 +6709,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46111</v>
+        <v>45436</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6720,7 +6725,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6763,7 +6768,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6777,10 +6782,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46128</v>
+        <v>45386</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6793,7 +6798,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6836,7 +6841,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6850,10 +6855,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46133</v>
+        <v>45164</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6866,7 +6871,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6909,7 +6914,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6923,10 +6928,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46155</v>
+        <v>44929</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6939,7 +6944,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>10.4</v>
+        <v>4.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6982,7 +6987,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6996,10 +7001,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46154</v>
+        <v>44977</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7012,7 +7017,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5</v>
+        <v>0.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7055,7 +7060,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7069,10 +7074,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46154</v>
+        <v>45761</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7085,7 +7090,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7128,7 +7133,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7142,10 +7147,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46157</v>
+        <v>45761</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7158,7 +7163,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7201,7 +7206,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7215,10 +7220,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46261</v>
+        <v>45761</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7231,7 +7236,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7274,7 +7279,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7288,10 +7293,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46266</v>
+        <v>45386</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7303,13 +7308,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7352,7 +7352,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7362,14 +7362,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46230</v>
+        <v>45319</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7425,7 +7425,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7439,10 +7439,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46243</v>
+        <v>45293</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>45006</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60261-2024</t>
+          <t>A 53422-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45642</v>
+        <v>45229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -861,147 +861,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 60261-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45642</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 53422-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44475</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44746</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>44472</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45366</v>
+        <v>44903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45386</v>
+        <v>44977</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1809,14 +1809,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45789</v>
+        <v>45293</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45635</v>
+        <v>45016</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46042</v>
+        <v>45894</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2018,7 +2018,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45894</v>
+        <v>45901</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 41381-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45173</v>
+        <v>45898</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45051</v>
+        <v>45905</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2247,14 +2247,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45673</v>
+        <v>45789</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41381-2025</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45898</v>
+        <v>44903</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45278</v>
+        <v>44903</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45901</v>
+        <v>46042</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45905</v>
+        <v>45910</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45910</v>
+        <v>45278</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46059</v>
+        <v>45915</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46059</v>
+        <v>45635</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46064</v>
+        <v>45051</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45915</v>
+        <v>45173</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45590</v>
+        <v>45673</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46070</v>
+        <v>46059</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46076</v>
+        <v>46059</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3196,14 +3196,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46076</v>
+        <v>45642</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45642</v>
+        <v>45229</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45642</v>
+        <v>46064</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45229</v>
+        <v>45642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3478,7 +3478,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45933</v>
+        <v>45642</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45642</v>
+        <v>45933</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46086</v>
+        <v>45188</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46086</v>
+        <v>46070</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>9.199999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
         <v>45847</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3853,14 +3853,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46090</v>
+        <v>46076</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46090</v>
+        <v>46076</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45155</v>
+        <v>46086</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46099</v>
+        <v>46086</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45016</v>
+        <v>46090</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46111</v>
+        <v>46090</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4291,14 +4291,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45182</v>
+        <v>45965</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46112</v>
+        <v>45436</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45965</v>
+        <v>45155</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4500,7 +4500,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45436</v>
+        <v>46099</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4573,7 +4573,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45980</v>
+        <v>45590</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4663,7 +4663,7 @@
         <v>45980</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46128</v>
+        <v>45980</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46133</v>
+        <v>45386</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44977</v>
+        <v>46112</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45852</v>
+        <v>46111</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45852</v>
+        <v>46128</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45859</v>
+        <v>46133</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38036-2025</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45881</v>
+        <v>45574</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46154</v>
+        <v>44977</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44903</v>
+        <v>45155</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46154</v>
+        <v>45852</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.4</v>
+        <v>0.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46155</v>
+        <v>45852</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>10.4</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45574</v>
+        <v>45761</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5609,10 +5609,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45541</v>
+        <v>45761</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45653</v>
+        <v>45761</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45155</v>
+        <v>45859</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5814,7 +5814,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45188</v>
+        <v>44497</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5887,7 +5887,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44903</v>
+        <v>45436</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44903</v>
+        <v>46155</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>10.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6033,7 +6033,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6047,10 +6047,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46261</v>
+        <v>46154</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6106,7 +6106,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6179,7 +6179,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46266</v>
+        <v>44929</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6208,13 +6208,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6257,7 +6252,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 38036-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6271,10 +6266,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46230</v>
+        <v>45881</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6287,7 +6282,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6330,7 +6325,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6344,10 +6339,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45436</v>
+        <v>45164</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6360,7 +6355,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6403,7 +6398,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6417,10 +6412,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44899</v>
+        <v>45653</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6433,7 +6428,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6476,7 +6471,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6490,10 +6485,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44977</v>
+        <v>45436</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6506,7 +6501,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6549,7 +6544,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6563,10 +6558,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44497</v>
+        <v>46157</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6579,7 +6574,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6622,7 +6617,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6636,10 +6631,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46243</v>
+        <v>46261</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6652,7 +6647,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6695,7 +6690,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6709,10 +6704,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45436</v>
+        <v>46266</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6724,8 +6719,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6768,7 +6768,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6782,10 +6782,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45386</v>
+        <v>44977</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6841,7 +6841,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6855,10 +6855,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45164</v>
+        <v>46230</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6914,7 +6914,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44929</v>
+        <v>46243</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6997,14 +6997,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44977</v>
+        <v>45182</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7060,7 +7060,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45761</v>
+        <v>45386</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7133,7 +7133,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45761</v>
+        <v>45366</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7206,7 +7206,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7216,14 +7216,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45761</v>
+        <v>45319</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7279,7 +7279,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45386</v>
+        <v>45541</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7352,7 +7352,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7362,14 +7362,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45319</v>
+        <v>45386</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7425,7 +7425,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7439,10 +7439,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45293</v>
+        <v>44899</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>45006</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>45229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>45642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44475</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44746</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>44472</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>44903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>44977</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>45293</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>45016</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>45894</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>45901</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45898</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>45905</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45789</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>44903</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>44903</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>46042</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>45910</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>45278</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45915</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>45635</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>45051</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>45173</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>45673</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>46059</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>46059</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45642</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>45229</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>46064</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>45642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>45642</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>45933</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>45188</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>46070</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45847</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>46076</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>46076</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>46086</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>46086</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>46090</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>46090</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>45965</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>45436</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>45155</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>46099</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>45590</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>45980</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>45980</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>45386</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>46112</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>46111</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>46128</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>46133</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>45574</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>44977</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>45155</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>45852</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45852</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>45761</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>45761</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>45761</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>45859</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>44497</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>45436</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>46155</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>46154</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>46154</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>44929</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>45881</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45164</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45653</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45436</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>46157</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>46261</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>46266</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>44977</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>46230</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>46243</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45182</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45386</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>45366</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45319</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45541</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>45386</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>44899</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>45006</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>45229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>45642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44475</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44746</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>44472</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>44497</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>44903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>44977</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>45293</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>45016</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>45894</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>45901</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45898</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>45905</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45789</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>44903</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>44903</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>46042</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>45910</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>45278</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45915</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>45635</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>45051</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>45173</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>45673</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>46059</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>46059</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45642</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>45229</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>46064</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>45642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>45642</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>45933</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>45188</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>46070</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45847</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>46076</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>46076</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>46086</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>46086</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>46090</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>46090</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>45965</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>45436</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>45155</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>46099</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>45590</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>45980</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>45980</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>45386</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>46112</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>46111</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>46128</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>46133</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>45574</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>44977</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>45155</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>45852</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45852</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>45761</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>45761</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>45761</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>45859</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>44497</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>45436</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>46155</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>46154</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>46154</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>44929</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>45881</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45164</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45653</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45436</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>46157</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>46261</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>46266</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>44977</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>46230</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>46243</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45182</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45386</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>45366</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45319</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45541</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>45386</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>44899</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>45006</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE94"/>
+  <dimension ref="A1:AE91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 53422-2023</t>
+          <t>A 60261-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45229</v>
+        <v>45642</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -861,147 +861,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 53422-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 60261-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45642</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44475</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44746</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 54313-2021</t>
+          <t>A 60972-2021</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1517,14 +1517,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44472</v>
+        <v>44497</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1580,7 +1580,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 60972-2021</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44497</v>
+        <v>45386</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44903</v>
+        <v>45366</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44977</v>
+        <v>45590</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45293</v>
+        <v>46042</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45016</v>
+        <v>45436</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45894</v>
+        <v>45673</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2018,7 +2018,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45901</v>
+        <v>45894</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 41381-2025</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45898</v>
+        <v>45901</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45905</v>
+        <v>45155</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2247,14 +2247,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45789</v>
+        <v>45905</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44903</v>
+        <v>45852</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44903</v>
+        <v>45852</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46042</v>
+        <v>45910</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45910</v>
+        <v>45859</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45278</v>
+        <v>45915</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45915</v>
+        <v>45016</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2758,14 +2758,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45635</v>
+        <v>45182</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45051</v>
+        <v>46059</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45173</v>
+        <v>46059</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45673</v>
+        <v>45642</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46059</v>
+        <v>45642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46059</v>
+        <v>46064</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45642</v>
+        <v>45229</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45229</v>
+        <v>45933</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46064</v>
+        <v>45642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45642</v>
+        <v>45847</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3478,7 +3478,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45642</v>
+        <v>46070</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45933</v>
+        <v>46076</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3624,7 +3624,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3634,14 +3634,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45188</v>
+        <v>46076</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46070</v>
+        <v>44977</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3770,7 +3770,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45847</v>
+        <v>46086</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3853,14 +3853,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46076</v>
+        <v>46090</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46086</v>
+        <v>45965</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>9.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46090</v>
+        <v>46099</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46090</v>
+        <v>46111</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45965</v>
+        <v>46112</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45436</v>
+        <v>45980</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45155</v>
+        <v>45980</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4500,7 +4500,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46099</v>
+        <v>46128</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4573,7 +4573,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45590</v>
+        <v>46133</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45980</v>
+        <v>44903</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45980</v>
+        <v>46154</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45386</v>
+        <v>46154</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46112</v>
+        <v>46155</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>10.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46111</v>
+        <v>45574</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46128</v>
+        <v>45541</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46133</v>
+        <v>45653</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45574</v>
+        <v>45155</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44977</v>
+        <v>45188</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45155</v>
+        <v>44903</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45852</v>
+        <v>44903</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45852</v>
+        <v>45436</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45761</v>
+        <v>46261</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5609,10 +5609,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45761</v>
+        <v>46157</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45761</v>
+        <v>44899</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45859</v>
+        <v>44977</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5831,7 +5831,7 @@
         <v>44497</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45436</v>
+        <v>46266</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5916,8 +5916,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5960,7 +5965,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5974,10 +5979,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46155</v>
+        <v>46230</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5990,7 +5995,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>10.4</v>
+        <v>3.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6033,7 +6038,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6047,10 +6052,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46154</v>
+        <v>45436</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6063,7 +6068,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6106,7 +6111,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6120,10 +6125,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46154</v>
+        <v>45386</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6136,7 +6141,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6179,7 +6184,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6193,10 +6198,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44929</v>
+        <v>45164</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6209,7 +6214,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6252,7 +6257,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 38036-2025</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6266,10 +6271,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45881</v>
+        <v>44929</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6282,7 +6287,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6325,7 +6330,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6339,10 +6344,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45164</v>
+        <v>44977</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6355,7 +6360,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6398,7 +6403,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6412,10 +6417,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45653</v>
+        <v>45761</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6428,7 +6433,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6471,7 +6476,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6485,10 +6490,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45436</v>
+        <v>45761</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6501,7 +6506,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6544,7 +6549,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6558,10 +6563,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46157</v>
+        <v>45761</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6574,7 +6579,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6617,7 +6622,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6631,10 +6636,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46261</v>
+        <v>46243</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6647,7 +6652,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6690,7 +6695,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6704,10 +6709,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46266</v>
+        <v>45386</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6719,13 +6724,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6768,7 +6768,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6778,14 +6778,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44977</v>
+        <v>45319</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6841,7 +6841,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6855,10 +6855,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46230</v>
+        <v>45293</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6914,7 +6914,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6924,14 +6924,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46243</v>
+        <v>45789</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6997,14 +6997,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45182</v>
+        <v>45635</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7060,7 +7060,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45386</v>
+        <v>45173</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7133,7 +7133,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45366</v>
+        <v>45051</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7206,7 +7206,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7216,14 +7216,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45319</v>
+        <v>45278</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7276,27 +7276,27 @@
       </c>
       <c r="V90" s="2" t="inlineStr"/>
     </row>
-    <row r="91" ht="15" customHeight="1">
+    <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>S 986-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45541</v>
+        <v>45006</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7308,8 +7308,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7348,230 +7353,6 @@
         <v>0</v>
       </c>
       <c r="V91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92" ht="15" customHeight="1">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>A 13250-2024</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="n">
-        <v>45386</v>
-      </c>
-      <c r="E92" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I92" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" t="n">
-        <v>0</v>
-      </c>
-      <c r="V92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>A 59223-2022</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="n">
-        <v>44899</v>
-      </c>
-      <c r="E93" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I93" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J93" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
-      <c r="R93" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" t="n">
-        <v>0</v>
-      </c>
-      <c r="V93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>S 986-2023</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D94" s="1" t="n">
-        <v>45006</v>
-      </c>
-      <c r="E94" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I94" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J94" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" t="n">
-        <v>0</v>
-      </c>
-      <c r="T94" t="n">
-        <v>0</v>
-      </c>
-      <c r="U94" t="n">
-        <v>0</v>
-      </c>
-      <c r="V94" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE91"/>
+  <dimension ref="A1:AE90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60261-2024</t>
+          <t>A 53422-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45642</v>
+        <v>45229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -861,147 +861,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 60261-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45642</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 53422-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 55213-2021</t>
+          <t>A 28159-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44475</v>
+        <v>44746</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28159-2022</t>
+          <t>A 60972-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1444,14 +1444,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44746</v>
+        <v>44497</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1507,7 +1507,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 60972-2021</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1517,14 +1517,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44497</v>
+        <v>44903</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1580,7 +1580,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45386</v>
+        <v>44977</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45366</v>
+        <v>45016</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45590</v>
+        <v>44903</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46042</v>
+        <v>44903</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45436</v>
+        <v>45173</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45673</v>
+        <v>46042</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2018,7 +2018,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45894</v>
+        <v>45188</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45901</v>
+        <v>45673</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45155</v>
+        <v>45894</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45905</v>
+        <v>45436</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45852</v>
+        <v>45901</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45852</v>
+        <v>46059</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.1</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45910</v>
+        <v>46059</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45859</v>
+        <v>45905</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45915</v>
+        <v>46064</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45016</v>
+        <v>45910</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2758,14 +2758,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45182</v>
+        <v>46070</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46059</v>
+        <v>45915</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2904,14 +2904,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46059</v>
+        <v>46076</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45642</v>
+        <v>46076</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45642</v>
+        <v>46086</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46064</v>
+        <v>46086</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45229</v>
+        <v>46090</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45933</v>
+        <v>46090</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3349,7 +3349,7 @@
         <v>45642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45847</v>
+        <v>45229</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3478,7 +3478,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46070</v>
+        <v>45155</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46076</v>
+        <v>45642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3624,7 +3624,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3634,14 +3634,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46076</v>
+        <v>45642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44977</v>
+        <v>45933</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3770,7 +3770,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46086</v>
+        <v>46099</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46086</v>
+        <v>45847</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>9.199999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46090</v>
+        <v>45590</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46090</v>
+        <v>45386</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45965</v>
+        <v>45852</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46099</v>
+        <v>45852</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46112</v>
+        <v>45859</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45980</v>
+        <v>46111</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45980</v>
+        <v>45965</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4517,7 +4517,7 @@
         <v>46128</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>46133</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44903</v>
+        <v>45574</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46154</v>
+        <v>44977</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46154</v>
+        <v>45980</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46155</v>
+        <v>45980</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>10.4</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45574</v>
+        <v>46155</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>10.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45541</v>
+        <v>46154</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45653</v>
+        <v>46154</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5174,7 +5174,7 @@
         <v>45155</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45188</v>
+        <v>45761</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44903</v>
+        <v>45761</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44903</v>
+        <v>45761</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45436</v>
+        <v>44497</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46261</v>
+        <v>45436</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5609,10 +5609,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46157</v>
+        <v>44929</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44899</v>
+        <v>46157</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44977</v>
+        <v>46261</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5814,7 +5814,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44497</v>
+        <v>45164</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5904,7 +5904,7 @@
         <v>46266</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46230</v>
+        <v>45653</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6038,7 +6038,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45436</v>
+        <v>46230</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45386</v>
+        <v>45436</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6184,7 +6184,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6198,10 +6198,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45164</v>
+        <v>46243</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6257,7 +6257,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6271,10 +6271,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44929</v>
+        <v>44977</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6330,7 +6330,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6340,14 +6340,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44977</v>
+        <v>45182</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6403,7 +6403,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45761</v>
+        <v>45386</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6476,7 +6476,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6490,10 +6490,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45761</v>
+        <v>45366</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6549,7 +6549,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6559,14 +6559,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45761</v>
+        <v>45319</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6622,7 +6622,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6636,10 +6636,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46243</v>
+        <v>45541</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6712,7 +6712,7 @@
         <v>45386</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6778,14 +6778,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45319</v>
+        <v>44899</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6858,7 +6858,7 @@
         <v>45293</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>45789</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45635</v>
+        <v>45278</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7060,7 +7060,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45173</v>
+        <v>45635</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7150,7 +7150,7 @@
         <v>45051</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7203,27 +7203,27 @@
       </c>
       <c r="V89" s="2" t="inlineStr"/>
     </row>
-    <row r="90" ht="15" customHeight="1">
+    <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>S 986-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45278</v>
+        <v>45006</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7235,8 +7235,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7275,84 +7280,6 @@
         <v>0</v>
       </c>
       <c r="V90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>S 986-2023</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="n">
-        <v>45006</v>
-      </c>
-      <c r="E91" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I91" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0</v>
-      </c>
-      <c r="S91" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 53422-2023</t>
+          <t>A 60261-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45229</v>
+        <v>45642</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -861,147 +861,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 53422-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 60261-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45642</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28159-2022</t>
+          <t>A 60972-2021</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44746</v>
+        <v>44497</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60972-2021</t>
+          <t>A 28159-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1444,14 +1444,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44497</v>
+        <v>44746</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1507,7 +1507,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44903</v>
+        <v>45293</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1580,7 +1580,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44977</v>
+        <v>45789</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45016</v>
+        <v>45366</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44903</v>
+        <v>45894</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1816,7 +1816,7 @@
         <v>44903</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45173</v>
+        <v>45635</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46042</v>
+        <v>45173</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2018,7 +2018,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45188</v>
+        <v>45051</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45673</v>
+        <v>45386</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45894</v>
+        <v>45278</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45436</v>
+        <v>45901</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45901</v>
+        <v>45905</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46059</v>
+        <v>45910</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46059</v>
+        <v>45915</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45905</v>
+        <v>45436</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46064</v>
+        <v>45642</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45910</v>
+        <v>45642</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46070</v>
+        <v>45229</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45915</v>
+        <v>45933</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2904,14 +2904,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46076</v>
+        <v>45642</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46076</v>
+        <v>45847</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46086</v>
+        <v>45590</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46086</v>
+        <v>45574</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>9.199999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46090</v>
+        <v>45852</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46090</v>
+        <v>45852</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45642</v>
+        <v>45859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45229</v>
+        <v>45541</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3478,7 +3478,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45155</v>
+        <v>45965</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45642</v>
+        <v>45155</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3624,7 +3624,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45642</v>
+        <v>45980</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45933</v>
+        <v>45016</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3770,7 +3770,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46099</v>
+        <v>45980</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45847</v>
+        <v>45653</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3926,14 +3926,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45590</v>
+        <v>45182</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45386</v>
+        <v>46154</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45852</v>
+        <v>46154</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.1</v>
+        <v>4.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45852</v>
+        <v>46155</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>10.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46112</v>
+        <v>45155</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45859</v>
+        <v>45188</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46111</v>
+        <v>44977</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45965</v>
+        <v>44903</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4500,7 +4500,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46128</v>
+        <v>44903</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4573,7 +4573,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46133</v>
+        <v>46042</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45574</v>
+        <v>45673</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44977</v>
+        <v>45436</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45980</v>
+        <v>46059</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45980</v>
+        <v>46059</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46155</v>
+        <v>46064</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>10.4</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46154</v>
+        <v>46070</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46154</v>
+        <v>44899</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45155</v>
+        <v>46076</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5240,14 +5240,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45761</v>
+        <v>46076</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45761</v>
+        <v>44977</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45761</v>
+        <v>44497</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44497</v>
+        <v>46086</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45436</v>
+        <v>46086</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5609,10 +5609,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44929</v>
+        <v>46090</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46157</v>
+        <v>46090</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46261</v>
+        <v>46099</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5814,7 +5814,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45164</v>
+        <v>45436</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5887,7 +5887,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46266</v>
+        <v>46111</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5916,13 +5916,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5965,7 +5960,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5979,10 +5974,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45653</v>
+        <v>45386</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5995,7 +5990,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6038,7 +6033,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6052,10 +6047,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46230</v>
+        <v>46112</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6068,7 +6063,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6111,7 +6106,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6125,10 +6120,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45436</v>
+        <v>45164</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6141,7 +6136,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6184,7 +6179,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6198,10 +6193,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46243</v>
+        <v>46128</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6214,7 +6209,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6257,7 +6252,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6271,10 +6266,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44977</v>
+        <v>44929</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6287,7 +6282,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6330,7 +6325,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6340,14 +6335,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45182</v>
+        <v>46261</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6360,7 +6355,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6403,7 +6398,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6417,10 +6412,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45386</v>
+        <v>44977</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6433,7 +6428,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6476,7 +6471,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6490,10 +6485,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45366</v>
+        <v>46157</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6506,7 +6501,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6549,7 +6544,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6559,14 +6554,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45319</v>
+        <v>45761</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6579,7 +6574,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6622,7 +6617,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6636,10 +6631,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45541</v>
+        <v>45761</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6652,7 +6647,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6695,7 +6690,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6709,10 +6704,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45386</v>
+        <v>45761</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6725,7 +6720,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6768,7 +6763,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6782,10 +6777,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44899</v>
+        <v>46133</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6841,7 +6836,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6855,10 +6850,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45293</v>
+        <v>46266</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6870,8 +6865,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6914,7 +6914,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6924,14 +6924,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45789</v>
+        <v>45386</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6997,14 +6997,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45278</v>
+        <v>45319</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7060,7 +7060,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45635</v>
+        <v>46230</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7133,7 +7133,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45051</v>
+        <v>46243</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7223,7 +7223,7 @@
         <v>45006</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE90"/>
+  <dimension ref="A1:AE91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60261-2024</t>
+          <t>A 53422-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45642</v>
+        <v>45229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -861,147 +861,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 60261-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45642</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 53422-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 60972-2021</t>
+          <t>A 28159-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44497</v>
+        <v>44746</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28159-2022</t>
+          <t>A 60972-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1444,14 +1444,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44746</v>
+        <v>44497</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1507,7 +1507,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45293</v>
+        <v>44903</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1580,7 +1580,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45789</v>
+        <v>44977</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45366</v>
+        <v>45016</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45894</v>
+        <v>44903</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1816,7 +1816,7 @@
         <v>44903</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45635</v>
+        <v>45188</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45173</v>
+        <v>46086</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2018,7 +2018,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45051</v>
+        <v>46086</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45386</v>
+        <v>46090</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>2.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45278</v>
+        <v>46090</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45901</v>
+        <v>45852</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45905</v>
+        <v>45852</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45910</v>
+        <v>45859</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45915</v>
+        <v>45155</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45436</v>
+        <v>45894</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45642</v>
+        <v>45901</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45642</v>
+        <v>45590</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45229</v>
+        <v>45386</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45933</v>
+        <v>45905</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45642</v>
+        <v>45910</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45847</v>
+        <v>45915</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45590</v>
+        <v>46099</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3130,7 +3130,7 @@
         <v>45574</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45852</v>
+        <v>45642</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45852</v>
+        <v>45229</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45859</v>
+        <v>45642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45541</v>
+        <v>45642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3478,7 +3478,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45965</v>
+        <v>45933</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45155</v>
+        <v>44977</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3624,7 +3624,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45980</v>
+        <v>46112</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45016</v>
+        <v>45847</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3770,7 +3770,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45980</v>
+        <v>45155</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45653</v>
+        <v>46111</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3926,14 +3926,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45182</v>
+        <v>45761</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46154</v>
+        <v>45761</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46154</v>
+        <v>45761</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46155</v>
+        <v>45965</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>10.4</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45155</v>
+        <v>44497</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45188</v>
+        <v>46128</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44977</v>
+        <v>45980</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44903</v>
+        <v>45980</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4500,7 +4500,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44903</v>
+        <v>46133</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4573,7 +4573,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46042</v>
+        <v>45436</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45673</v>
+        <v>44929</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45436</v>
+        <v>46042</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46059</v>
+        <v>45164</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46059</v>
+        <v>45673</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46064</v>
+        <v>46059</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46070</v>
+        <v>46059</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44899</v>
+        <v>46064</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46076</v>
+        <v>46070</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
         <v>46076</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44977</v>
+        <v>46076</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44497</v>
+        <v>45653</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46086</v>
+        <v>46155</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>10.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46086</v>
+        <v>46154</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5609,10 +5609,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46090</v>
+        <v>45436</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46090</v>
+        <v>46154</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46099</v>
+        <v>44977</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5814,7 +5814,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5824,14 +5824,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45436</v>
+        <v>45182</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5887,7 +5887,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46111</v>
+        <v>45386</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45386</v>
+        <v>46157</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6033,7 +6033,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6047,10 +6047,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46112</v>
+        <v>45366</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45164</v>
+        <v>46266</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6135,8 +6135,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6179,7 +6184,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6189,14 +6194,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46128</v>
+        <v>45319</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6209,7 +6214,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6252,7 +6257,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6266,10 +6271,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44929</v>
+        <v>45541</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6282,7 +6287,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6325,7 +6330,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6339,10 +6344,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46261</v>
+        <v>46230</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6355,7 +6360,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6398,7 +6403,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6412,10 +6417,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44977</v>
+        <v>45386</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6428,7 +6433,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6471,7 +6476,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6485,10 +6490,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46157</v>
+        <v>44899</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6501,7 +6506,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6544,7 +6549,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6558,10 +6563,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45761</v>
+        <v>45293</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6574,7 +6579,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6617,7 +6622,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6631,10 +6636,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45761</v>
+        <v>46243</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6647,7 +6652,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6690,7 +6695,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6700,14 +6705,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45761</v>
+        <v>45789</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6720,7 +6725,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6763,7 +6768,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6777,10 +6782,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46133</v>
+        <v>45278</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6793,7 +6798,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6836,7 +6841,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6850,10 +6855,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46266</v>
+        <v>45635</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6865,13 +6870,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6914,7 +6914,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45386</v>
+        <v>45051</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6997,14 +6997,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45319</v>
+        <v>45173</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7060,7 +7060,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46230</v>
+        <v>45436</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7133,7 +7133,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 42006-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46243</v>
+        <v>46303</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7203,83 +7203,156 @@
       </c>
       <c r="V89" s="2" t="inlineStr"/>
     </row>
-    <row r="90">
+    <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
+          <t>A 35402-2026</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E90" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>S 986-2023</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D90" s="1" t="n">
+      <c r="D91" s="1" t="n">
         <v>45006</v>
       </c>
-      <c r="E90" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
+      <c r="E91" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I90" t="n">
+      <c r="I91" t="n">
         <v>0.9</v>
       </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" s="2" t="inlineStr"/>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 53422-2023</t>
+          <t>A 60261-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45229</v>
+        <v>45642</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -861,147 +861,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 53422-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 60261-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45642</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44746</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44497</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44903</v>
+        <v>44929</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>44977</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45016</v>
+        <v>45761</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44903</v>
+        <v>45761</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44903</v>
+        <v>45761</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45188</v>
+        <v>44903</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46086</v>
+        <v>45366</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2018,7 +2018,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46086</v>
+        <v>45386</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46090</v>
+        <v>45386</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2174,14 +2174,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46090</v>
+        <v>45319</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45852</v>
+        <v>45894</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45852</v>
+        <v>45901</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45859</v>
+        <v>45905</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45155</v>
+        <v>45910</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45894</v>
+        <v>45590</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45901</v>
+        <v>45915</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45590</v>
+        <v>45293</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2758,14 +2758,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45386</v>
+        <v>45789</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45905</v>
+        <v>45574</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45910</v>
+        <v>45635</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45915</v>
+        <v>45155</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46099</v>
+        <v>45541</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45574</v>
+        <v>45173</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45642</v>
+        <v>45051</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45229</v>
+        <v>45278</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3349,7 +3349,7 @@
         <v>45642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3422,7 +3422,7 @@
         <v>45642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3478,7 +3478,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45933</v>
+        <v>45229</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44977</v>
+        <v>45933</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3624,7 +3624,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46112</v>
+        <v>45642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45847</v>
+        <v>45016</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3770,7 +3770,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3780,14 +3780,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45155</v>
+        <v>45182</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46111</v>
+        <v>45847</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45761</v>
+        <v>45653</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45761</v>
+        <v>45436</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45761</v>
+        <v>45155</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45965</v>
+        <v>45188</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44497</v>
+        <v>45965</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46128</v>
+        <v>44977</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45980</v>
+        <v>45852</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45980</v>
+        <v>44903</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4500,7 +4500,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46133</v>
+        <v>44903</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4573,7 +4573,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45436</v>
+        <v>45852</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44929</v>
+        <v>45859</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46042</v>
+        <v>45980</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45164</v>
+        <v>45980</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45673</v>
+        <v>46099</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46059</v>
+        <v>46111</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46059</v>
+        <v>45436</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46064</v>
+        <v>46112</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46070</v>
+        <v>46128</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5240,14 +5240,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46076</v>
+        <v>44899</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46076</v>
+        <v>44977</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45653</v>
+        <v>46133</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46155</v>
+        <v>44497</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>10.4</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46154</v>
+        <v>45436</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5609,10 +5609,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45436</v>
+        <v>46042</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46154</v>
+        <v>45386</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44977</v>
+        <v>45673</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5814,7 +5814,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5824,14 +5824,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45182</v>
+        <v>45164</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45386</v>
+        <v>46059</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46157</v>
+        <v>46059</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6033,7 +6033,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6047,10 +6047,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45366</v>
+        <v>46064</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46266</v>
+        <v>46070</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6135,13 +6135,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6184,7 +6179,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6194,14 +6189,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45319</v>
+        <v>46076</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6214,7 +6209,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6257,7 +6252,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6267,14 +6262,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45541</v>
+        <v>46076</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6287,7 +6282,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6330,7 +6325,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6344,10 +6339,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46230</v>
+        <v>46154</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6360,7 +6355,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6403,7 +6398,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6417,10 +6412,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45386</v>
+        <v>46154</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6433,7 +6428,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6476,7 +6471,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6490,10 +6485,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44899</v>
+        <v>46155</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6506,7 +6501,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>10.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6549,7 +6544,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6563,10 +6558,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45293</v>
+        <v>46086</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6579,7 +6574,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6622,7 +6617,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6636,10 +6631,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46243</v>
+        <v>46086</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6652,7 +6647,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6695,7 +6690,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6705,14 +6700,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45789</v>
+        <v>46090</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6725,7 +6720,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6768,7 +6763,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6782,10 +6777,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45278</v>
+        <v>46090</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6798,7 +6793,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6841,7 +6836,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6855,10 +6850,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45635</v>
+        <v>46157</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6871,7 +6866,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6914,7 +6909,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6928,10 +6923,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45051</v>
+        <v>46266</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6943,8 +6938,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45173</v>
+        <v>46230</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7060,7 +7060,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45436</v>
+        <v>46243</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>46303</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>46261</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45006</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -620,41 +620,42 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva
+          <t>Blanksvart trämyra
+Svart trolldruva
 Blåsippa</t>
         </is>
       </c>
@@ -707,7 +708,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -812,7 +813,7 @@
         <v>45642</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -917,7 +918,7 @@
         <v>45229</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1022,7 +1023,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,7 +1128,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,7 +1233,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,7 +1306,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1379,7 @@
         <v>44746</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1451,7 +1452,7 @@
         <v>44497</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1524,7 +1525,7 @@
         <v>44929</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1597,7 +1598,7 @@
         <v>44977</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1670,7 +1671,7 @@
         <v>45761</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1743,7 +1744,7 @@
         <v>45761</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1816,7 +1817,7 @@
         <v>45761</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1889,7 +1890,7 @@
         <v>44903</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1962,7 +1963,7 @@
         <v>45366</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2035,7 +2036,7 @@
         <v>45386</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2108,7 +2109,7 @@
         <v>45386</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2181,7 +2182,7 @@
         <v>45319</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2254,7 +2255,7 @@
         <v>45894</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2327,7 +2328,7 @@
         <v>45901</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2400,7 +2401,7 @@
         <v>45905</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2473,7 +2474,7 @@
         <v>45910</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2546,7 +2547,7 @@
         <v>45590</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2619,7 +2620,7 @@
         <v>45915</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2692,7 +2693,7 @@
         <v>45293</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2765,7 +2766,7 @@
         <v>45789</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2838,7 +2839,7 @@
         <v>45574</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2911,7 +2912,7 @@
         <v>45635</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2984,7 +2985,7 @@
         <v>45155</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3057,7 +3058,7 @@
         <v>45541</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3130,7 +3131,7 @@
         <v>45173</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3203,7 +3204,7 @@
         <v>45051</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3276,7 +3277,7 @@
         <v>45278</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3349,7 +3350,7 @@
         <v>45642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3422,7 +3423,7 @@
         <v>45642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3495,7 +3496,7 @@
         <v>45229</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3568,7 +3569,7 @@
         <v>45933</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3641,7 +3642,7 @@
         <v>45642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3714,7 +3715,7 @@
         <v>45016</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3787,7 +3788,7 @@
         <v>45182</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3860,7 +3861,7 @@
         <v>45847</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3933,7 +3934,7 @@
         <v>45653</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4006,7 +4007,7 @@
         <v>45436</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4079,7 +4080,7 @@
         <v>45155</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4152,7 +4153,7 @@
         <v>45188</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4225,7 +4226,7 @@
         <v>45965</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4298,7 +4299,7 @@
         <v>44977</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4371,7 +4372,7 @@
         <v>45852</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4444,7 +4445,7 @@
         <v>44903</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4517,7 +4518,7 @@
         <v>44903</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4590,7 +4591,7 @@
         <v>45852</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4663,7 +4664,7 @@
         <v>45859</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4736,7 +4737,7 @@
         <v>45980</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4809,7 +4810,7 @@
         <v>45980</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4882,7 +4883,7 @@
         <v>46099</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4955,7 +4956,7 @@
         <v>46111</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5028,7 +5029,7 @@
         <v>45436</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5101,7 +5102,7 @@
         <v>46112</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5174,7 +5175,7 @@
         <v>46128</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5247,7 +5248,7 @@
         <v>44899</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5320,7 +5321,7 @@
         <v>44977</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5393,7 +5394,7 @@
         <v>46133</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5466,7 +5467,7 @@
         <v>44497</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5539,7 +5540,7 @@
         <v>45436</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5612,7 +5613,7 @@
         <v>46042</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5685,7 +5686,7 @@
         <v>45386</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5758,7 +5759,7 @@
         <v>45673</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5831,7 +5832,7 @@
         <v>45164</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5904,7 +5905,7 @@
         <v>46059</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5977,7 +5978,7 @@
         <v>46059</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6050,7 +6051,7 @@
         <v>46064</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6123,7 +6124,7 @@
         <v>46070</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6196,7 +6197,7 @@
         <v>46076</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6269,7 +6270,7 @@
         <v>46076</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6342,7 +6343,7 @@
         <v>46154</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6415,7 +6416,7 @@
         <v>46154</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6488,7 +6489,7 @@
         <v>46155</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6561,7 +6562,7 @@
         <v>46086</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6634,7 +6635,7 @@
         <v>46086</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6707,7 +6708,7 @@
         <v>46090</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6780,7 +6781,7 @@
         <v>46090</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6853,7 +6854,7 @@
         <v>46157</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6926,7 +6927,7 @@
         <v>46266</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7004,7 +7005,7 @@
         <v>46230</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7077,7 +7078,7 @@
         <v>46243</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7150,7 +7151,7 @@
         <v>46303</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7223,7 +7224,7 @@
         <v>46261</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7296,7 +7297,7 @@
         <v>45006</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>45642</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45229</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44746</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>44497</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>44929</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44977</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>45761</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>45761</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>45761</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>44903</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45366</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>45386</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45386</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>45319</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>45894</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>45901</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>45905</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>45910</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>45590</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>45915</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>45293</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>45789</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>45574</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>45635</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45155</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>45541</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>45173</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45051</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>45278</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>45642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>45229</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>45933</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>45642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>45016</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>45182</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>45847</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>45653</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>45436</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>45155</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>45188</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>45965</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>44977</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>45852</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44903</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>44903</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>45852</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>45859</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>45980</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>45980</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>46099</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>46111</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45436</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>46112</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>46128</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>44899</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>44977</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>46133</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>44497</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>45436</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>46042</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>45386</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45673</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>45164</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         <v>46059</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>46059</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>46064</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>46070</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>46076</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>46076</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>46154</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>46154</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>46155</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>46086</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>46086</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>46090</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>46090</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>46157</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>46266</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>46230</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>46243</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>46303</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>46261</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>45006</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60261-2024</t>
+          <t>A 53422-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45642</v>
+        <v>45229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -862,147 +862,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 60261-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45642</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 53422-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44746</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>44497</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44929</v>
+        <v>45894</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1581,7 +1581,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44977</v>
+        <v>45901</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45761</v>
+        <v>45905</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1727,7 +1727,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1741,10 +1741,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45761</v>
+        <v>45366</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45761</v>
+        <v>45910</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1873,7 +1873,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44903</v>
+        <v>45915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45366</v>
+        <v>44903</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2019,7 +2019,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2029,14 +2029,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45386</v>
+        <v>45319</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>0.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2092,7 +2092,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45386</v>
+        <v>45541</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2165,7 +2165,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2175,14 +2175,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45319</v>
+        <v>45642</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2238,7 +2238,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45894</v>
+        <v>45229</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2311,7 +2311,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45901</v>
+        <v>45642</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45905</v>
+        <v>45642</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45910</v>
+        <v>45933</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2530,7 +2530,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45590</v>
+        <v>45847</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45915</v>
+        <v>45386</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45293</v>
+        <v>44899</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2749,7 +2749,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2759,14 +2759,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45789</v>
+        <v>45965</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2822,7 +2822,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45574</v>
+        <v>45293</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45635</v>
+        <v>45980</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45155</v>
+        <v>45980</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3041,7 +3041,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45541</v>
+        <v>45789</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45173</v>
+        <v>46157</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3187,7 +3187,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45051</v>
+        <v>45278</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3260,7 +3260,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45278</v>
+        <v>45635</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3333,7 +3333,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45642</v>
+        <v>46266</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3362,8 +3362,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3406,7 +3411,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3420,10 +3425,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45642</v>
+        <v>45051</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3436,7 +3441,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3479,7 +3484,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3493,10 +3498,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45229</v>
+        <v>45173</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3509,7 +3514,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3552,7 +3557,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3566,10 +3571,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45933</v>
+        <v>44977</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3582,7 +3587,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3625,7 +3630,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3639,10 +3644,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45642</v>
+        <v>46230</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3655,7 +3660,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3698,7 +3703,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3712,10 +3717,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45016</v>
+        <v>45436</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3728,7 +3733,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3771,7 +3776,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3781,14 +3786,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45182</v>
+        <v>46042</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3801,7 +3806,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3844,7 +3849,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3858,10 +3863,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45847</v>
+        <v>45852</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3874,7 +3879,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.4</v>
+        <v>0.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3917,7 +3922,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3931,10 +3936,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45653</v>
+        <v>45852</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3947,7 +3952,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3990,7 +3995,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4004,10 +4009,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45436</v>
+        <v>46243</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4063,7 +4068,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4077,10 +4082,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45155</v>
+        <v>45673</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4093,7 +4098,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4136,7 +4141,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4150,10 +4155,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45188</v>
+        <v>45859</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4166,7 +4171,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4209,7 +4214,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4223,10 +4228,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45965</v>
+        <v>46059</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4239,7 +4244,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4282,7 +4287,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4296,10 +4301,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44977</v>
+        <v>46059</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4312,7 +4317,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4355,7 +4360,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4369,10 +4374,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45852</v>
+        <v>46064</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4385,7 +4390,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4428,7 +4433,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4442,10 +4447,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44903</v>
+        <v>46070</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4458,7 +4463,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4501,7 +4506,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4511,14 +4516,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44903</v>
+        <v>46076</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4531,7 +4536,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4574,7 +4579,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4588,10 +4593,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45852</v>
+        <v>46076</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4604,7 +4609,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4647,7 +4652,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4661,10 +4666,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45859</v>
+        <v>45016</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4677,7 +4682,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4720,7 +4725,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4734,10 +4739,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45980</v>
+        <v>46086</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4750,7 +4755,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4793,7 +4798,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4807,10 +4812,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45980</v>
+        <v>46086</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4823,7 +4828,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4866,7 +4871,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4880,10 +4885,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46099</v>
+        <v>46090</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4896,7 +4901,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4939,7 +4944,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4953,10 +4958,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46111</v>
+        <v>46090</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4969,7 +4974,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5012,7 +5017,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5026,10 +5031,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45436</v>
+        <v>46099</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5042,7 +5047,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5102,7 +5107,7 @@
         <v>46112</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5158,7 +5163,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5172,10 +5177,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46128</v>
+        <v>46111</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5188,7 +5193,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5231,7 +5236,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 42006-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5245,10 +5250,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44899</v>
+        <v>46303</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5261,7 +5266,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5304,7 +5309,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5318,10 +5323,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44977</v>
+        <v>44903</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5334,7 +5339,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5377,7 +5382,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5391,10 +5396,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46133</v>
+        <v>44903</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5407,7 +5412,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5450,7 +5455,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5464,10 +5469,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44497</v>
+        <v>46128</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5480,7 +5485,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5523,7 +5528,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5537,10 +5542,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45436</v>
+        <v>46133</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5553,7 +5558,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5596,7 +5601,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5610,10 +5615,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46042</v>
+        <v>46261</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5626,7 +5631,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5669,7 +5674,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5683,10 +5688,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45386</v>
+        <v>45188</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5699,7 +5704,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5742,7 +5747,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5756,10 +5761,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45673</v>
+        <v>45155</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5772,7 +5777,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5815,7 +5820,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5829,10 +5834,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45164</v>
+        <v>46155</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5845,7 +5850,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>10.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5888,7 +5893,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5902,10 +5907,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46059</v>
+        <v>46154</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5918,7 +5923,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5961,7 +5966,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5975,10 +5980,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46059</v>
+        <v>45590</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5991,7 +5996,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6034,7 +6039,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6048,10 +6053,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46064</v>
+        <v>46154</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6064,7 +6069,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6107,7 +6112,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6121,10 +6126,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46070</v>
+        <v>45386</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6137,7 +6142,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6180,7 +6185,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6194,10 +6199,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46076</v>
+        <v>45574</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6210,7 +6215,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6253,7 +6258,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6263,14 +6268,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46076</v>
+        <v>44977</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6283,7 +6288,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6326,7 +6331,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6340,10 +6345,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46154</v>
+        <v>45155</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6356,7 +6361,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6399,7 +6404,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6413,10 +6418,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46154</v>
+        <v>45761</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6429,7 +6434,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6472,7 +6477,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6486,10 +6491,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46155</v>
+        <v>45761</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6502,7 +6507,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>10.4</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6545,7 +6550,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6559,10 +6564,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46086</v>
+        <v>45761</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6575,7 +6580,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6618,7 +6623,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6632,10 +6637,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46086</v>
+        <v>44497</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6648,7 +6653,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>9.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6691,7 +6696,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6705,10 +6710,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46090</v>
+        <v>45436</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6721,7 +6726,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6764,7 +6769,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6778,10 +6783,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46090</v>
+        <v>44929</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6794,7 +6799,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6837,7 +6842,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6851,10 +6856,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46157</v>
+        <v>45164</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6867,7 +6872,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6910,7 +6915,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6924,10 +6929,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46266</v>
+        <v>45653</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6939,13 +6944,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6988,7 +6988,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46230</v>
+        <v>45436</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7061,7 +7061,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46243</v>
+        <v>44977</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7134,7 +7134,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 42006-2026</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7144,14 +7144,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46303</v>
+        <v>45182</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.2</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7207,7 +7207,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7221,10 +7221,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46261</v>
+        <v>45386</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7297,7 +7297,7 @@
         <v>45006</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 53422-2023</t>
+          <t>A 60261-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45229</v>
+        <v>45642</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -862,147 +862,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 53422-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 60261-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45642</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44746</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>44497</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45894</v>
+        <v>45366</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1581,7 +1581,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1591,14 +1591,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45901</v>
+        <v>45789</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45905</v>
+        <v>45386</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1727,7 +1727,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1741,10 +1741,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45366</v>
+        <v>45635</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45910</v>
+        <v>45173</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1873,7 +1873,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45915</v>
+        <v>45051</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44903</v>
+        <v>45278</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2019,7 +2019,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2029,14 +2029,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45319</v>
+        <v>45894</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2092,7 +2092,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45541</v>
+        <v>45901</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2165,7 +2165,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45642</v>
+        <v>45905</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2238,7 +2238,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45229</v>
+        <v>45436</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45642</v>
+        <v>45910</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45642</v>
+        <v>45915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45933</v>
+        <v>45590</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2530,7 +2530,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45847</v>
+        <v>45642</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45386</v>
+        <v>45642</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44899</v>
+        <v>45229</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2749,7 +2749,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45965</v>
+        <v>45933</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2822,7 +2822,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45293</v>
+        <v>45642</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45980</v>
+        <v>45847</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45980</v>
+        <v>45852</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3041,7 +3041,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45789</v>
+        <v>45852</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46157</v>
+        <v>45859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3187,7 +3187,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45278</v>
+        <v>46042</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3260,7 +3260,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45635</v>
+        <v>45155</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3333,7 +3333,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46266</v>
+        <v>45673</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3362,13 +3362,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3411,7 +3406,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3425,10 +3420,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45051</v>
+        <v>45965</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3441,7 +3436,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3484,7 +3479,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3498,10 +3493,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45173</v>
+        <v>45016</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3514,7 +3509,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3557,7 +3552,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3567,14 +3562,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44977</v>
+        <v>45182</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3587,7 +3582,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3630,7 +3625,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3644,10 +3639,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46230</v>
+        <v>45980</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3660,7 +3655,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3703,7 +3698,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3717,10 +3712,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45436</v>
+        <v>45980</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3733,7 +3728,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3776,7 +3771,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3790,10 +3785,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46042</v>
+        <v>46059</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3806,7 +3801,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3849,7 +3844,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3863,10 +3858,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45852</v>
+        <v>46059</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3879,7 +3874,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.1</v>
+        <v>2.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3922,7 +3917,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3936,10 +3931,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45852</v>
+        <v>46064</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3952,7 +3947,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3995,7 +3990,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4009,10 +4004,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46243</v>
+        <v>46070</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4025,7 +4020,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4068,7 +4063,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4082,10 +4077,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45673</v>
+        <v>46076</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4098,7 +4093,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4141,7 +4136,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4151,14 +4146,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45859</v>
+        <v>46076</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4171,7 +4166,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4214,7 +4209,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4228,10 +4223,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46059</v>
+        <v>44977</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4244,7 +4239,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4287,7 +4282,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4301,10 +4296,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46059</v>
+        <v>46086</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4317,7 +4312,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4360,7 +4355,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4374,10 +4369,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46064</v>
+        <v>46086</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4390,7 +4385,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4433,7 +4428,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4447,10 +4442,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46070</v>
+        <v>46090</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4463,7 +4458,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4506,7 +4501,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4516,14 +4511,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46076</v>
+        <v>46090</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4536,7 +4531,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4579,7 +4574,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4593,10 +4588,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46076</v>
+        <v>46099</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4609,7 +4604,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4652,7 +4647,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4666,10 +4661,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45016</v>
+        <v>46111</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4682,7 +4677,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4725,7 +4720,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4739,10 +4734,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46086</v>
+        <v>46112</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4755,7 +4750,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4798,7 +4793,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4812,10 +4807,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46086</v>
+        <v>46128</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4828,7 +4823,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>9.199999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4871,7 +4866,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4885,10 +4880,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46090</v>
+        <v>46133</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4901,7 +4896,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4944,7 +4939,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4958,10 +4953,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46090</v>
+        <v>44903</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4974,7 +4969,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5017,7 +5012,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5031,10 +5026,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46099</v>
+        <v>45574</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5047,7 +5042,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5090,7 +5085,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5104,10 +5099,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46112</v>
+        <v>46154</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5120,7 +5115,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5163,7 +5158,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5177,10 +5172,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46111</v>
+        <v>46154</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5193,7 +5188,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5236,7 +5231,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 42006-2026</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5250,10 +5245,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46303</v>
+        <v>45541</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5266,7 +5261,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.2</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5309,7 +5304,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5323,10 +5318,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44903</v>
+        <v>46155</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5339,7 +5334,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>10.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5382,7 +5377,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5396,10 +5391,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44903</v>
+        <v>45653</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5455,7 +5450,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5469,10 +5464,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46128</v>
+        <v>45155</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5485,7 +5480,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5528,7 +5523,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5542,10 +5537,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46133</v>
+        <v>45188</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5558,7 +5553,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5601,7 +5596,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5615,10 +5610,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46261</v>
+        <v>44903</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5631,7 +5626,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5674,7 +5669,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5688,10 +5683,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45188</v>
+        <v>44903</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5704,7 +5699,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5747,7 +5742,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5761,10 +5756,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45155</v>
+        <v>45436</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5777,7 +5772,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5820,7 +5815,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5834,10 +5829,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46155</v>
+        <v>44899</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5850,7 +5845,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>10.4</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5893,7 +5888,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5907,10 +5902,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46154</v>
+        <v>44977</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5923,7 +5918,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5966,7 +5961,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5980,10 +5975,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45590</v>
+        <v>44497</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5996,7 +5991,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6039,7 +6034,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6053,10 +6048,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6069,7 +6064,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6112,7 +6107,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6126,10 +6121,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45386</v>
+        <v>46230</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6142,7 +6137,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6185,7 +6180,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6199,10 +6194,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45574</v>
+        <v>45436</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6215,7 +6210,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6258,7 +6253,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6272,10 +6267,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44977</v>
+        <v>45386</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6288,7 +6283,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6331,7 +6326,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6345,10 +6340,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45155</v>
+        <v>45164</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6361,7 +6356,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6404,7 +6399,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6418,10 +6413,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45761</v>
+        <v>44929</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6434,7 +6429,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6477,7 +6472,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6491,10 +6486,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45761</v>
+        <v>44977</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6507,7 +6502,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6550,7 +6545,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6567,7 +6562,7 @@
         <v>45761</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6580,7 +6575,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6623,7 +6618,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6637,10 +6632,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44497</v>
+        <v>45761</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6653,7 +6648,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6696,7 +6691,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6710,10 +6705,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45436</v>
+        <v>45761</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6726,7 +6721,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6769,7 +6764,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6783,10 +6778,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44929</v>
+        <v>46243</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6799,7 +6794,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6842,7 +6837,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6856,10 +6851,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45164</v>
+        <v>45386</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6915,7 +6910,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6925,14 +6920,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45653</v>
+        <v>45319</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6945,7 +6940,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6988,7 +6983,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7002,10 +6997,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45436</v>
+        <v>45293</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7018,7 +7013,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7061,7 +7056,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 42006-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7075,10 +7070,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44977</v>
+        <v>46303</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7091,7 +7086,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7134,7 +7129,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7144,14 +7139,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45182</v>
+        <v>46261</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7164,7 +7159,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7207,7 +7202,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7221,10 +7216,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45386</v>
+        <v>46266</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7236,8 +7231,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7297,7 +7297,7 @@
         <v>45006</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60261-2024</t>
+          <t>A 53422-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45642</v>
+        <v>45229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -862,147 +862,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 60261-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45642</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 53422-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44746</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60972-2021</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1445,14 +1445,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44497</v>
+        <v>45278</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1508,7 +1508,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45366</v>
+        <v>45635</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1581,7 +1581,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1591,14 +1591,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45789</v>
+        <v>45761</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45386</v>
+        <v>45761</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1727,7 +1727,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1741,10 +1741,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45635</v>
+        <v>45761</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45173</v>
+        <v>45051</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1873,7 +1873,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 60972-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1883,14 +1883,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45051</v>
+        <v>44497</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45278</v>
+        <v>45173</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2019,7 +2019,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45894</v>
+        <v>44903</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2092,7 +2092,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45901</v>
+        <v>44497</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2165,7 +2165,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45905</v>
+        <v>45436</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2238,7 +2238,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45436</v>
+        <v>44977</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2311,7 +2311,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45910</v>
+        <v>45894</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45915</v>
+        <v>45901</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45590</v>
+        <v>45852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2530,7 +2530,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45642</v>
+        <v>45852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45642</v>
+        <v>45905</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45229</v>
+        <v>45859</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2749,7 +2749,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45933</v>
+        <v>45910</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2822,7 +2822,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45642</v>
+        <v>45915</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45847</v>
+        <v>45016</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45852</v>
+        <v>45436</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3041,7 +3041,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45852</v>
+        <v>44903</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45859</v>
+        <v>44903</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3187,7 +3187,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46042</v>
+        <v>45642</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3260,7 +3260,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45155</v>
+        <v>45229</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45673</v>
+        <v>45642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3406,7 +3406,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45965</v>
+        <v>45642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45016</v>
+        <v>45933</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3562,14 +3562,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45182</v>
+        <v>46070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45980</v>
+        <v>45847</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3698,7 +3698,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3708,14 +3708,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45980</v>
+        <v>46076</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3771,7 +3771,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46059</v>
+        <v>46076</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3858,10 +3858,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46059</v>
+        <v>46086</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3917,7 +3917,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46064</v>
+        <v>46086</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46070</v>
+        <v>46090</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4063,7 +4063,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46076</v>
+        <v>46090</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4146,14 +4146,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46076</v>
+        <v>45188</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4209,7 +4209,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44977</v>
+        <v>45965</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46086</v>
+        <v>46099</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4355,7 +4355,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4369,10 +4369,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46086</v>
+        <v>46112</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>9.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4428,7 +4428,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46090</v>
+        <v>45980</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4501,7 +4501,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46090</v>
+        <v>46111</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46099</v>
+        <v>45980</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4647,7 +4647,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46111</v>
+        <v>45155</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.3</v>
+        <v>0.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4720,7 +4720,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4793,7 +4793,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4807,10 +4807,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46128</v>
+        <v>46133</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4866,7 +4866,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46133</v>
+        <v>45590</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4939,7 +4939,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44903</v>
+        <v>45386</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5029,7 +5029,7 @@
         <v>45574</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46154</v>
+        <v>44977</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5158,7 +5158,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46154</v>
+        <v>46042</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5231,7 +5231,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45541</v>
+        <v>45155</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5304,7 +5304,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46155</v>
+        <v>45673</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>10.4</v>
+        <v>2.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5377,7 +5377,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45653</v>
+        <v>46059</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5450,7 +5450,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5464,10 +5464,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45155</v>
+        <v>46059</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5523,7 +5523,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45188</v>
+        <v>44929</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5596,7 +5596,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5610,10 +5610,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44903</v>
+        <v>46064</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44903</v>
+        <v>46155</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>10.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5742,7 +5742,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5756,10 +5756,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45436</v>
+        <v>46154</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5815,7 +5815,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44899</v>
+        <v>45164</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5888,7 +5888,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5902,10 +5902,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44977</v>
+        <v>46154</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5961,7 +5961,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44497</v>
+        <v>45653</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6048,10 +6048,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46157</v>
+        <v>45436</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46230</v>
+        <v>44977</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6194,10 +6194,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45436</v>
+        <v>46157</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6253,7 +6253,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45386</v>
+        <v>46230</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6326,7 +6326,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45164</v>
+        <v>46243</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6399,7 +6399,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6409,14 +6409,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44929</v>
+        <v>45182</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6472,7 +6472,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6486,10 +6486,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44977</v>
+        <v>45386</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6545,7 +6545,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6559,10 +6559,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45761</v>
+        <v>45366</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6618,7 +6618,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6628,14 +6628,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45761</v>
+        <v>45319</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45761</v>
+        <v>45541</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6764,7 +6764,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46243</v>
+        <v>45386</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6837,7 +6837,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 42006-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45386</v>
+        <v>46303</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6910,7 +6910,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6920,14 +6920,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45319</v>
+        <v>44899</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6997,10 +6997,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45293</v>
+        <v>46261</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7056,7 +7056,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 42006-2026</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46303</v>
+        <v>45293</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>6.2</v>
+        <v>2.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7129,7 +7129,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46261</v>
+        <v>46266</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7158,8 +7158,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7202,7 +7207,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7212,14 +7217,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46266</v>
+        <v>45789</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7231,13 +7236,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7297,7 +7297,7 @@
         <v>45006</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE91"/>
+  <dimension ref="A1:AE93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 53422-2023</t>
+          <t>A 5311-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45229</v>
+        <v>44594</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -826,23 +826,23 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
@@ -850,51 +850,51 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 5311-2022 artfynd.xlsx", "A 5311-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 5311-2022 karta.png", "A 5311-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 5311-2022 georefererad karta.tif", "A 5311-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 5311-2022 FSC-klagomål.docx", "A 5311-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 5311-2022 FSC-klagomål mail.docx", "A 5311-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 5311-2022 tillsynsbegäran.docx", "A 5311-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 5311-2022 tillsynsbegäran mail.docx", "A 5311-2022")</f>
         <v/>
       </c>
     </row>
@@ -918,7 +918,7 @@
         <v>45642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 61174-2025</t>
+          <t>A 53422-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46000</v>
+        <v>45229</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1060,7 +1060,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1072,147 +1072,147 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 61174-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46000</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Nordbjörnbär</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 61174-2025 artfynd.xlsx", "A 61174-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 61174-2025 karta.png", "A 61174-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 61174-2025 georefererad karta.tif", "A 61174-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 61174-2025 FSC-klagomål.docx", "A 61174-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 61174-2025 FSC-klagomål mail.docx", "A 61174-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 61174-2025 tillsynsbegäran.docx", "A 61174-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 61174-2025 tillsynsbegäran mail.docx", "A 61174-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 5311-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44594</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 5311-2022 artfynd.xlsx", "A 5311-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 5311-2022 karta.png", "A 5311-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 5311-2022 georefererad karta.tif", "A 5311-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 5311-2022 FSC-klagomål.docx", "A 5311-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 5311-2022 FSC-klagomål mail.docx", "A 5311-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 5311-2022 tillsynsbegäran.docx", "A 5311-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 5311-2022 tillsynsbegäran mail.docx", "A 5311-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44746</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 60972-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1445,14 +1445,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45278</v>
+        <v>44497</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1508,7 +1508,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45635</v>
+        <v>45436</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1581,7 +1581,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45761</v>
+        <v>45366</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45761</v>
+        <v>44903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1727,7 +1727,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1741,10 +1741,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45761</v>
+        <v>45386</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45051</v>
+        <v>45852</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1873,7 +1873,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60972-2021</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1883,14 +1883,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44497</v>
+        <v>45852</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45173</v>
+        <v>45859</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2019,7 +2019,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44903</v>
+        <v>45894</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2092,7 +2092,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44497</v>
+        <v>45590</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2165,7 +2165,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45436</v>
+        <v>46099</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2238,7 +2238,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44977</v>
+        <v>45901</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2311,7 +2311,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45894</v>
+        <v>46111</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45901</v>
+        <v>46112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45852</v>
+        <v>45155</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2530,7 +2530,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45852</v>
+        <v>45574</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45905</v>
+        <v>46128</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45859</v>
+        <v>45541</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2749,7 +2749,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45910</v>
+        <v>46133</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2822,7 +2822,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45915</v>
+        <v>45016</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45016</v>
+        <v>45905</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2978,14 +2978,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45436</v>
+        <v>45182</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3041,7 +3041,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44903</v>
+        <v>45653</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44903</v>
+        <v>45910</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3187,7 +3187,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45642</v>
+        <v>44977</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3260,7 +3260,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45229</v>
+        <v>45155</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3333,7 +3333,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45642</v>
+        <v>45188</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3406,7 +3406,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45642</v>
+        <v>46154</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45933</v>
+        <v>44903</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46070</v>
+        <v>44903</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45847</v>
+        <v>45915</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3698,7 +3698,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3708,14 +3708,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46076</v>
+        <v>46154</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3771,7 +3771,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46076</v>
+        <v>46155</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>10.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3858,10 +3858,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46086</v>
+        <v>45436</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3917,7 +3917,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46086</v>
+        <v>45642</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>9.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46090</v>
+        <v>45642</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4063,7 +4063,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46090</v>
+        <v>45229</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45188</v>
+        <v>44899</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4209,7 +4209,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45965</v>
+        <v>45933</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46099</v>
+        <v>45642</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4355,7 +4355,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4369,10 +4369,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46112</v>
+        <v>44977</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4428,7 +4428,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45980</v>
+        <v>44497</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4501,7 +4501,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46111</v>
+        <v>45847</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45980</v>
+        <v>45436</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4647,7 +4647,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45155</v>
+        <v>45386</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4720,7 +4720,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46128</v>
+        <v>45164</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4793,7 +4793,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4807,10 +4807,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46133</v>
+        <v>46157</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4866,7 +4866,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45590</v>
+        <v>44929</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4939,7 +4939,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45386</v>
+        <v>44977</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45574</v>
+        <v>45761</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5085,7 +5085,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44977</v>
+        <v>45761</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5158,7 +5158,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46042</v>
+        <v>45761</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5231,7 +5231,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45155</v>
+        <v>46230</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5304,7 +5304,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45673</v>
+        <v>45965</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5377,7 +5377,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46059</v>
+        <v>45386</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5450,7 +5450,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5460,14 +5460,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46059</v>
+        <v>45319</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5523,7 +5523,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44929</v>
+        <v>46243</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5596,7 +5596,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5610,10 +5610,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46064</v>
+        <v>45980</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46155</v>
+        <v>45980</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>10.4</v>
+        <v>2.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5742,7 +5742,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5756,10 +5756,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46154</v>
+        <v>45293</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5815,7 +5815,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5825,14 +5825,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45164</v>
+        <v>45789</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5888,7 +5888,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5902,10 +5902,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46154</v>
+        <v>45635</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5961,7 +5961,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45653</v>
+        <v>45173</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6048,10 +6048,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45436</v>
+        <v>45051</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44977</v>
+        <v>45278</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 42006-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6194,10 +6194,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46157</v>
+        <v>46303</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6253,7 +6253,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46230</v>
+        <v>46261</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6326,7 +6326,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46243</v>
+        <v>46042</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6409,14 +6409,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45182</v>
+        <v>45673</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6472,7 +6472,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6486,10 +6486,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45386</v>
+        <v>46059</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6545,7 +6545,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6559,10 +6559,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45366</v>
+        <v>46059</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6618,7 +6618,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 42964-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6628,14 +6628,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45319</v>
+        <v>46310</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 42968-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45541</v>
+        <v>46310</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6764,7 +6764,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45386</v>
+        <v>46266</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6793,8 +6793,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6837,7 +6842,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 42006-2026</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6851,10 +6856,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46303</v>
+        <v>46064</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6867,7 +6872,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>6.2</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6910,7 +6915,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6924,10 +6929,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44899</v>
+        <v>46070</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6940,7 +6945,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6983,7 +6988,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6997,10 +7002,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46261</v>
+        <v>46076</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7013,7 +7018,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7056,7 +7061,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7066,14 +7071,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45293</v>
+        <v>46076</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7086,7 +7091,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7129,7 +7134,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7143,10 +7148,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46266</v>
+        <v>46086</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7158,13 +7163,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7207,7 +7207,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7217,14 +7217,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45789</v>
+        <v>46086</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7277,83 +7277,229 @@
       </c>
       <c r="V90" s="2" t="inlineStr"/>
     </row>
-    <row r="91">
+    <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
+          <t>A 12532-2026</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D91" s="1" t="n">
+        <v>46090</v>
+      </c>
+      <c r="E91" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>A 12523-2026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="n">
+        <v>46090</v>
+      </c>
+      <c r="E92" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>2</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>S 986-2023</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D91" s="1" t="n">
+      <c r="D93" s="1" t="n">
         <v>45006</v>
       </c>
-      <c r="E91" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
+      <c r="E93" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I91" t="n">
+      <c r="I93" t="n">
         <v>0.9</v>
       </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0</v>
-      </c>
-      <c r="S91" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" s="2" t="inlineStr"/>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 5311-2022</t>
+          <t>A 53422-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44594</v>
+        <v>45229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -841,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -850,51 +850,51 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 5311-2022 artfynd.xlsx", "A 5311-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 5311-2022 karta.png", "A 5311-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 5311-2022 georefererad karta.tif", "A 5311-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 5311-2022 FSC-klagomål.docx", "A 5311-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 5311-2022 FSC-klagomål mail.docx", "A 5311-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 5311-2022 tillsynsbegäran.docx", "A 5311-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 5311-2022 tillsynsbegäran mail.docx", "A 5311-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
     </row>
@@ -918,7 +918,7 @@
         <v>45642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 53422-2023</t>
+          <t>A 61174-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45229</v>
+        <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1036,17 +1036,17 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1072,46 +1072,46 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Nordbjörnbär</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 61174-2025 artfynd.xlsx", "A 61174-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 61174-2025 karta.png", "A 61174-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 61174-2025 georefererad karta.tif", "A 61174-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 61174-2025 FSC-klagomål.docx", "A 61174-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 61174-2025 FSC-klagomål mail.docx", "A 61174-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 61174-2025 tillsynsbegäran.docx", "A 61174-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 61174-2025 tillsynsbegäran mail.docx", "A 61174-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 61174-2025</t>
+          <t>A 5311-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1125,10 +1125,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46000</v>
+        <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1168,48 +1168,48 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Nordbjörnbär</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 61174-2025 artfynd.xlsx", "A 61174-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 5311-2022 artfynd.xlsx", "A 5311-2022")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 61174-2025 karta.png", "A 61174-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 5311-2022 karta.png", "A 5311-2022")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 61174-2025 georefererad karta.tif", "A 61174-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 5311-2022 georefererad karta.tif", "A 5311-2022")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 61174-2025 FSC-klagomål.docx", "A 61174-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 5311-2022 FSC-klagomål.docx", "A 5311-2022")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 61174-2025 FSC-klagomål mail.docx", "A 61174-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 5311-2022 FSC-klagomål mail.docx", "A 5311-2022")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 61174-2025 tillsynsbegäran.docx", "A 61174-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 5311-2022 tillsynsbegäran.docx", "A 5311-2022")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 61174-2025 tillsynsbegäran mail.docx", "A 61174-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 5311-2022 tillsynsbegäran mail.docx", "A 5311-2022")</f>
         <v/>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44746</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>44497</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45436</v>
+        <v>44903</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45366</v>
+        <v>44977</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44903</v>
+        <v>45016</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1727,7 +1727,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1741,10 +1741,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45386</v>
+        <v>44903</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>0.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45852</v>
+        <v>44903</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1873,7 +1873,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45852</v>
+        <v>45188</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.1</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45859</v>
+        <v>45155</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2019,7 +2019,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45894</v>
+        <v>45590</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2092,7 +2092,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45590</v>
+        <v>45386</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2165,7 +2165,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46099</v>
+        <v>45894</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2238,7 +2238,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45901</v>
+        <v>45574</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2311,7 +2311,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46111</v>
+        <v>45901</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46112</v>
+        <v>45905</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45155</v>
+        <v>44977</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2530,7 +2530,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45574</v>
+        <v>45910</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46128</v>
+        <v>45915</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45541</v>
+        <v>45155</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2749,7 +2749,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46133</v>
+        <v>45642</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2822,7 +2822,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45016</v>
+        <v>45229</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45905</v>
+        <v>45642</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2978,14 +2978,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45182</v>
+        <v>45642</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3041,7 +3041,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45653</v>
+        <v>45933</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45910</v>
+        <v>45761</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3187,7 +3187,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44977</v>
+        <v>45761</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3260,7 +3260,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45155</v>
+        <v>45761</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3333,7 +3333,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45188</v>
+        <v>45847</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3406,7 +3406,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5</v>
+        <v>10.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44903</v>
+        <v>46154</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44903</v>
+        <v>44497</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45915</v>
+        <v>46154</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3698,7 +3698,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46154</v>
+        <v>45965</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3771,7 +3771,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46155</v>
+        <v>45436</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>10.4</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3858,10 +3858,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45436</v>
+        <v>45980</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3917,7 +3917,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45642</v>
+        <v>45980</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45642</v>
+        <v>44929</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4063,7 +4063,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45229</v>
+        <v>45164</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44899</v>
+        <v>46042</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4209,7 +4209,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45933</v>
+        <v>45673</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45642</v>
+        <v>46059</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4355,7 +4355,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4369,10 +4369,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44977</v>
+        <v>46059</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4428,7 +4428,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44497</v>
+        <v>45653</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4501,7 +4501,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45847</v>
+        <v>46064</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45436</v>
+        <v>46070</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4647,7 +4647,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4657,14 +4657,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45386</v>
+        <v>46076</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4720,7 +4720,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45164</v>
+        <v>46076</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4793,7 +4793,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4807,10 +4807,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46157</v>
+        <v>46086</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4866,7 +4866,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44929</v>
+        <v>46086</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4939,7 +4939,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44977</v>
+        <v>46090</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45761</v>
+        <v>46090</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5085,7 +5085,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45761</v>
+        <v>45436</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5158,7 +5158,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45761</v>
+        <v>46099</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5231,7 +5231,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46230</v>
+        <v>46112</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5304,7 +5304,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45965</v>
+        <v>46111</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5377,7 +5377,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45386</v>
+        <v>44977</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5450,7 +5450,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5460,14 +5460,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45319</v>
+        <v>46128</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5523,7 +5523,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46243</v>
+        <v>46133</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5596,7 +5596,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5610,10 +5610,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45980</v>
+        <v>46157</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45980</v>
+        <v>46230</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5742,7 +5742,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5752,14 +5752,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45293</v>
+        <v>45182</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5815,7 +5815,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5825,14 +5825,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45789</v>
+        <v>45386</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5888,7 +5888,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5902,10 +5902,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45635</v>
+        <v>46243</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5961,7 +5961,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45173</v>
+        <v>45366</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6044,14 +6044,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45051</v>
+        <v>45319</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45278</v>
+        <v>45541</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 42006-2026</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6194,10 +6194,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46303</v>
+        <v>45386</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.2</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6253,7 +6253,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46261</v>
+        <v>44899</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6326,7 +6326,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 42006-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46042</v>
+        <v>46303</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6399,7 +6399,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45673</v>
+        <v>45293</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6472,7 +6472,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6482,14 +6482,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46059</v>
+        <v>45789</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6545,7 +6545,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6559,10 +6559,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46059</v>
+        <v>45278</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6618,7 +6618,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 42964-2026</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46310</v>
+        <v>45635</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 42968-2026</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46310</v>
+        <v>45051</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6764,7 +6764,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46266</v>
+        <v>46261</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6793,13 +6793,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6842,7 +6837,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6856,10 +6851,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46064</v>
+        <v>45173</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6872,7 +6867,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6915,7 +6910,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6929,10 +6924,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46070</v>
+        <v>46266</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6944,8 +6939,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6988,7 +6988,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 42964-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46076</v>
+        <v>46310</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7061,7 +7061,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 42968-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7071,14 +7071,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46076</v>
+        <v>46310</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7134,7 +7134,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46086</v>
+        <v>45436</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7207,7 +7207,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7221,10 +7221,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46086</v>
+        <v>45852</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>9.199999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7294,10 +7294,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46090</v>
+        <v>45852</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7353,7 +7353,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46090</v>
+        <v>45859</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7443,7 +7443,7 @@
         <v>45006</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>45229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44746</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>44497</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>44903</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44977</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>45016</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>44903</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>44903</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>45188</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45155</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>45590</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45386</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>45894</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>45574</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>45901</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>45905</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>44977</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>45910</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>45915</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>45155</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>45642</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>45229</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>45642</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45642</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>45933</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>45761</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45761</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>45761</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>45847</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>46155</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>46154</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>44497</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>46154</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>45965</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>45436</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>45980</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>45980</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>44929</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>45164</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>46042</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>45673</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>46059</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>46059</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>45653</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>46064</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>46070</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>46076</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>46076</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>46086</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>46086</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>46090</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>46090</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>45436</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>46099</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>46112</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>46111</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>44977</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>46128</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>46133</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>46157</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>46230</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45182</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>45386</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         <v>46243</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>45366</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>45319</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>45541</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>45386</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>44899</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>46303</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>45293</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>45789</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>45278</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>45635</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>45051</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>46261</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>45173</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>46266</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>46310</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>46310</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>45436</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>45852</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>45852</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>45859</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>45006</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>45229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44746</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>44497</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>44903</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44977</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>45016</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>44903</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>44903</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>45188</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45155</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>45590</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45386</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>45894</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>45574</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>45901</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>45905</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>44977</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>45910</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>45915</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>45155</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>45642</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>45229</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>45642</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45642</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>45933</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>45761</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45761</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>45761</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>45847</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>46155</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>46154</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>44497</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>46154</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>45965</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>45436</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>45980</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>45980</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>44929</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>45164</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>46042</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>45673</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>46059</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>46059</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>45653</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>46064</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>46070</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>46076</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>46076</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>46086</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>46086</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>46090</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>46090</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>45436</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>46099</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>46112</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>46111</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>44977</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>46128</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>46133</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>46157</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>46230</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45182</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>45386</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         <v>46243</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>45366</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>45319</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>45541</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>45386</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>44899</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>46303</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>45293</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>45789</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>45278</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>45635</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>45051</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>46261</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>45173</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>46266</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>46310</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>46310</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>45436</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>45852</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>45852</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>45859</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>45006</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 53422-2023</t>
+          <t>A 60261-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45229</v>
+        <v>45642</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -862,147 +862,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 53422-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 60261-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45642</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44746</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>44497</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44903</v>
+        <v>45386</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1581,7 +1581,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44977</v>
+        <v>45366</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45016</v>
+        <v>45590</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1727,7 +1727,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1741,10 +1741,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44903</v>
+        <v>45155</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44903</v>
+        <v>45016</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1873,7 +1873,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1883,14 +1883,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45188</v>
+        <v>45182</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45155</v>
+        <v>44977</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2019,7 +2019,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45590</v>
+        <v>45894</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2092,7 +2092,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45386</v>
+        <v>45901</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2165,7 +2165,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45894</v>
+        <v>45905</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2238,7 +2238,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45574</v>
+        <v>45910</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2311,7 +2311,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45901</v>
+        <v>45915</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45905</v>
+        <v>45642</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44977</v>
+        <v>45642</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2530,7 +2530,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45910</v>
+        <v>45229</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45915</v>
+        <v>45933</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45155</v>
+        <v>45642</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2749,7 +2749,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45642</v>
+        <v>45847</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2822,7 +2822,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45229</v>
+        <v>44903</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45642</v>
+        <v>46154</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45642</v>
+        <v>46154</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3041,7 +3041,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45933</v>
+        <v>46155</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>10.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45761</v>
+        <v>45965</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3187,7 +3187,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45761</v>
+        <v>45980</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3260,7 +3260,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45761</v>
+        <v>45980</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3333,7 +3333,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45847</v>
+        <v>45574</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3406,7 +3406,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46155</v>
+        <v>45541</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>10.4</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46154</v>
+        <v>46042</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44497</v>
+        <v>45673</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46154</v>
+        <v>45653</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3698,7 +3698,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45965</v>
+        <v>46059</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3771,7 +3771,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45436</v>
+        <v>46059</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3858,10 +3858,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45980</v>
+        <v>46064</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3917,7 +3917,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45980</v>
+        <v>46070</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44929</v>
+        <v>46076</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4063,7 +4063,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4073,14 +4073,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45164</v>
+        <v>46076</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46042</v>
+        <v>45155</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4209,7 +4209,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45673</v>
+        <v>45188</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46059</v>
+        <v>46086</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4355,7 +4355,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4369,10 +4369,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46059</v>
+        <v>46086</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4428,7 +4428,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45653</v>
+        <v>46090</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4501,7 +4501,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46064</v>
+        <v>46090</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46070</v>
+        <v>44903</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4647,7 +4647,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4657,14 +4657,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46076</v>
+        <v>44903</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4720,7 +4720,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46076</v>
+        <v>46099</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4793,7 +4793,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4807,10 +4807,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46086</v>
+        <v>46111</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4866,7 +4866,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46086</v>
+        <v>46112</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>9.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4939,7 +4939,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46090</v>
+        <v>46128</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46090</v>
+        <v>46133</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5085,7 +5085,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5102,7 +5102,7 @@
         <v>45436</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5158,7 +5158,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46099</v>
+        <v>44899</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5231,7 +5231,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46112</v>
+        <v>44977</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5304,7 +5304,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46111</v>
+        <v>44497</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5377,7 +5377,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44977</v>
+        <v>46157</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5450,7 +5450,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5464,10 +5464,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46128</v>
+        <v>46230</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5523,7 +5523,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46133</v>
+        <v>45436</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5596,7 +5596,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5610,10 +5610,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46157</v>
+        <v>45386</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46230</v>
+        <v>45164</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5742,7 +5742,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5752,14 +5752,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45182</v>
+        <v>44929</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5815,7 +5815,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45386</v>
+        <v>44977</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5888,7 +5888,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5902,10 +5902,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46243</v>
+        <v>45761</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5961,7 +5961,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45366</v>
+        <v>45761</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6044,14 +6044,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45319</v>
+        <v>45761</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45541</v>
+        <v>46243</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6197,7 +6197,7 @@
         <v>45386</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6263,14 +6263,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44899</v>
+        <v>45319</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6326,7 +6326,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 42006-2026</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46303</v>
+        <v>45293</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>6.2</v>
+        <v>2.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6399,7 +6399,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6409,14 +6409,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45293</v>
+        <v>45789</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6472,7 +6472,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6482,14 +6482,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45789</v>
+        <v>45635</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6545,7 +6545,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6559,10 +6559,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45278</v>
+        <v>45173</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6618,7 +6618,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45635</v>
+        <v>45051</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45051</v>
+        <v>45278</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6764,7 +6764,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 42006-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46261</v>
+        <v>46303</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6837,7 +6837,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45173</v>
+        <v>46261</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6910,7 +6910,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46266</v>
+        <v>45436</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6939,13 +6939,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7005,7 +7000,7 @@
         <v>46310</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7078,7 +7073,7 @@
         <v>46310</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7134,7 +7129,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7148,10 +7143,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45436</v>
+        <v>46266</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7163,8 +7158,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7207,7 +7207,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7224,7 +7224,7 @@
         <v>45852</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7297,7 +7297,7 @@
         <v>45852</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7370,7 +7370,7 @@
         <v>45859</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>45006</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60261-2024</t>
+          <t>A 53422-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45642</v>
+        <v>45229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -862,147 +862,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 60261-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45642</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 53422-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44746</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>44497</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45386</v>
+        <v>44903</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1581,7 +1581,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45366</v>
+        <v>44977</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1664,14 +1664,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45590</v>
+        <v>45789</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1727,7 +1727,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1741,10 +1741,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45155</v>
+        <v>45278</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45016</v>
+        <v>45635</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1873,7 +1873,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1883,14 +1883,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45182</v>
+        <v>45051</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44977</v>
+        <v>45173</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2019,7 +2019,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45894</v>
+        <v>45016</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45901</v>
+        <v>45894</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2165,7 +2165,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45905</v>
+        <v>45436</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2238,7 +2238,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45910</v>
+        <v>45901</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2311,7 +2311,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45915</v>
+        <v>45905</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45642</v>
+        <v>44903</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45642</v>
+        <v>44903</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2530,7 +2530,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45229</v>
+        <v>45910</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45933</v>
+        <v>46042</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45642</v>
+        <v>45915</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2749,7 +2749,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45847</v>
+        <v>45673</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2822,7 +2822,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44903</v>
+        <v>46059</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46154</v>
+        <v>46059</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46154</v>
+        <v>46064</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3041,7 +3041,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46155</v>
+        <v>45642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>10.4</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45965</v>
+        <v>45229</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3187,7 +3187,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45980</v>
+        <v>45642</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3260,7 +3260,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45980</v>
+        <v>45642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3333,7 +3333,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45574</v>
+        <v>46070</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3406,7 +3406,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45541</v>
+        <v>45933</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46042</v>
+        <v>45188</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3562,14 +3562,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45673</v>
+        <v>46076</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45653</v>
+        <v>46076</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3698,7 +3698,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46059</v>
+        <v>45847</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3771,7 +3771,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46059</v>
+        <v>46086</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3858,10 +3858,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46064</v>
+        <v>46086</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3917,7 +3917,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46070</v>
+        <v>46090</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46076</v>
+        <v>46090</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4063,7 +4063,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4073,14 +4073,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46076</v>
+        <v>46099</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45155</v>
+        <v>45965</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4209,7 +4209,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45188</v>
+        <v>46112</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46086</v>
+        <v>45155</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4355,7 +4355,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4369,10 +4369,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46086</v>
+        <v>46111</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>9.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4428,7 +4428,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46090</v>
+        <v>45590</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4501,7 +4501,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46090</v>
+        <v>46128</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44903</v>
+        <v>45980</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4647,7 +4647,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44903</v>
+        <v>45386</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4720,7 +4720,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46099</v>
+        <v>45980</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4793,7 +4793,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4807,10 +4807,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46111</v>
+        <v>46133</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4866,7 +4866,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46112</v>
+        <v>45852</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4939,7 +4939,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46128</v>
+        <v>45852</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46133</v>
+        <v>45859</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5085,7 +5085,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45436</v>
+        <v>45574</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5158,7 +5158,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44899</v>
+        <v>44977</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5231,7 +5231,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44977</v>
+        <v>45155</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5304,7 +5304,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44497</v>
+        <v>45761</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5377,7 +5377,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46157</v>
+        <v>45761</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5450,7 +5450,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5464,10 +5464,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46230</v>
+        <v>45761</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5523,7 +5523,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45436</v>
+        <v>44497</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5596,7 +5596,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5610,10 +5610,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45386</v>
+        <v>46155</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>10.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45164</v>
+        <v>46154</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5742,7 +5742,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5756,10 +5756,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44929</v>
+        <v>46154</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5815,7 +5815,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44977</v>
+        <v>45436</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5888,7 +5888,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5902,10 +5902,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45761</v>
+        <v>44929</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5961,7 +5961,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45761</v>
+        <v>45164</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6048,10 +6048,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45761</v>
+        <v>45653</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46243</v>
+        <v>46157</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6194,10 +6194,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45386</v>
+        <v>46230</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6253,7 +6253,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6263,14 +6263,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45319</v>
+        <v>45436</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6326,7 +6326,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45293</v>
+        <v>44977</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6399,7 +6399,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6409,14 +6409,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45789</v>
+        <v>46243</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6472,7 +6472,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6482,14 +6482,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45635</v>
+        <v>45182</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6545,7 +6545,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 42006-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6559,10 +6559,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45173</v>
+        <v>46303</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.3</v>
+        <v>6.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6618,7 +6618,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45051</v>
+        <v>45386</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45278</v>
+        <v>46261</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6764,7 +6764,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 42006-2026</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46303</v>
+        <v>46266</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6793,8 +6793,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>6.2</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6837,7 +6842,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 42964-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6851,10 +6856,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46261</v>
+        <v>46310</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6867,7 +6872,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6910,7 +6915,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 42968-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6924,10 +6929,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45436</v>
+        <v>46310</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6940,7 +6945,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6983,7 +6988,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 42964-2026</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6997,10 +7002,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46310</v>
+        <v>45366</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7013,7 +7018,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7056,7 +7061,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 42968-2026</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7066,14 +7071,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46310</v>
+        <v>45319</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7086,7 +7091,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7129,7 +7134,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7143,10 +7148,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46266</v>
+        <v>45541</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7158,13 +7163,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7207,7 +7207,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7221,10 +7221,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45852</v>
+        <v>45386</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7294,10 +7294,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45852</v>
+        <v>44899</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7353,7 +7353,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45859</v>
+        <v>45293</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7443,7 +7443,7 @@
         <v>45006</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 53422-2023</t>
+          <t>A 60261-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45229</v>
+        <v>45642</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -862,147 +862,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 53422-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 60261-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45642</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44746</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>44497</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44903</v>
+        <v>45366</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1581,7 +1581,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1591,14 +1591,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44977</v>
+        <v>45789</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1664,14 +1664,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45789</v>
+        <v>45386</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1727,7 +1727,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1741,10 +1741,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45278</v>
+        <v>45635</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45635</v>
+        <v>45173</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
         <v>45051</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45173</v>
+        <v>45278</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2019,7 +2019,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45016</v>
+        <v>45894</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45894</v>
+        <v>45901</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2165,7 +2165,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45436</v>
+        <v>45905</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2238,7 +2238,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45901</v>
+        <v>45910</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2311,7 +2311,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45905</v>
+        <v>45436</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44903</v>
+        <v>45915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44903</v>
+        <v>45590</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2530,7 +2530,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45910</v>
+        <v>45642</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46042</v>
+        <v>45642</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45915</v>
+        <v>45229</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2749,7 +2749,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45673</v>
+        <v>45933</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2822,7 +2822,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46059</v>
+        <v>45642</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46059</v>
+        <v>45847</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46064</v>
+        <v>45852</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3041,7 +3041,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45642</v>
+        <v>45852</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45229</v>
+        <v>45859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3187,7 +3187,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45642</v>
+        <v>45155</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3260,7 +3260,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45642</v>
+        <v>45016</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3333,7 +3333,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46070</v>
+        <v>45965</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3406,7 +3406,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3416,14 +3416,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45933</v>
+        <v>45182</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45188</v>
+        <v>46042</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3562,14 +3562,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46076</v>
+        <v>45980</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46076</v>
+        <v>45980</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3698,7 +3698,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45847</v>
+        <v>45673</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3771,7 +3771,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46086</v>
+        <v>44977</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3858,10 +3858,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46086</v>
+        <v>46059</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>9.199999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3917,7 +3917,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46090</v>
+        <v>46059</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46090</v>
+        <v>46064</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4063,7 +4063,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46099</v>
+        <v>46070</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45965</v>
+        <v>46076</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4209,7 +4209,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4219,14 +4219,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46112</v>
+        <v>46076</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45155</v>
+        <v>46086</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4355,7 +4355,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4369,10 +4369,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46111</v>
+        <v>46086</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4428,7 +4428,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45590</v>
+        <v>46090</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4501,7 +4501,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46128</v>
+        <v>46090</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45980</v>
+        <v>46099</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4647,7 +4647,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45386</v>
+        <v>46111</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4720,7 +4720,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45980</v>
+        <v>46112</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4793,7 +4793,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4807,10 +4807,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46133</v>
+        <v>44903</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4866,7 +4866,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45852</v>
+        <v>46128</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4939,7 +4939,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45852</v>
+        <v>46133</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45859</v>
+        <v>45574</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5085,7 +5085,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45574</v>
+        <v>45541</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5158,7 +5158,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44977</v>
+        <v>46154</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5231,7 +5231,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45155</v>
+        <v>46154</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5304,7 +5304,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 18138-2025</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45761</v>
+        <v>46155</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>10.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5377,7 +5377,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18142-2025</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45761</v>
+        <v>45653</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5450,7 +5450,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18143-2025</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5464,10 +5464,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45761</v>
+        <v>45155</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5523,7 +5523,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44497</v>
+        <v>45188</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5596,7 +5596,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5610,10 +5610,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46155</v>
+        <v>44903</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46154</v>
+        <v>44903</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5742,7 +5742,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5756,10 +5756,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46154</v>
+        <v>45436</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5815,7 +5815,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45436</v>
+        <v>44899</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5888,7 +5888,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5902,10 +5902,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44929</v>
+        <v>44977</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5961,7 +5961,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45164</v>
+        <v>44497</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6048,10 +6048,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45653</v>
+        <v>46157</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46157</v>
+        <v>45436</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6197,7 +6197,7 @@
         <v>46230</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45436</v>
+        <v>45386</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6326,7 +6326,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44977</v>
+        <v>45164</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6399,7 +6399,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46243</v>
+        <v>44929</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6472,7 +6472,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6482,14 +6482,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45182</v>
+        <v>44977</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6545,7 +6545,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 42006-2026</t>
+          <t>A 18138-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6559,10 +6559,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46303</v>
+        <v>45761</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>6.2</v>
+        <v>0.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6618,7 +6618,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 18142-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45386</v>
+        <v>45761</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 18143-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46261</v>
+        <v>45761</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6764,7 +6764,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46266</v>
+        <v>46243</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6793,13 +6793,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6842,7 +6837,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 42964-2026</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6856,10 +6851,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46310</v>
+        <v>45386</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6872,7 +6867,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6915,7 +6910,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 42968-2026</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6925,14 +6920,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46310</v>
+        <v>45319</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6945,7 +6940,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6988,7 +6983,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7002,10 +6997,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45366</v>
+        <v>45293</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7018,7 +7013,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7061,7 +7056,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 42006-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7071,14 +7066,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45319</v>
+        <v>46303</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7091,7 +7086,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>6.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7134,7 +7129,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7148,10 +7143,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45541</v>
+        <v>46261</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7164,7 +7159,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7207,7 +7202,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 42964-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7221,10 +7216,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45386</v>
+        <v>46310</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7237,7 +7232,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7280,7 +7275,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 42968-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7294,10 +7289,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44899</v>
+        <v>46310</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7310,7 +7305,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7353,7 +7348,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7367,10 +7362,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45293</v>
+        <v>46266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7382,8 +7377,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7443,7 +7443,7 @@
         <v>45006</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60261-2024</t>
+          <t>A 53422-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45642</v>
+        <v>45229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -862,147 +862,147 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 60261-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45642</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LYSEKIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 60261-2024 artfynd.xlsx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 60261-2024 karta.png", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 60261-2024 georefererad karta.tif", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 60261-2024 FSC-klagomål.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 60261-2024 FSC-klagomål mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 60261-2024 tillsynsbegäran.docx", "A 60261-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 60261-2024 tillsynsbegäran mail.docx", "A 60261-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 53422-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LYSEKIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/artfynd/A 53422-2023 artfynd.xlsx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor/A 53422-2023 karta.png", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/kartor_geotiff/A 53422-2023 georefererad karta.tif", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomål/A 53422-2023 FSC-klagomål.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/klagomålsmail/A 53422-2023 FSC-klagomål mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsyn/A 53422-2023 tillsynsbegäran.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1484/tillsynsmail/A 53422-2023 tillsynsbegäran mail.docx", "A 53422-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>46000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>44594</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>44498</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>44529</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44746</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>44497</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 10579-2024</t>
+          <t>A 41581-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45366</v>
+        <v>45173</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1581,7 +1581,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 22605-2025</t>
+          <t>A 61991-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1591,14 +1591,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45789</v>
+        <v>45653</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 13246-2024</t>
+          <t>A 58793-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45386</v>
+        <v>44903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1727,7 +1727,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 58619-2024</t>
+          <t>A 8474-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1741,10 +1741,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45635</v>
+        <v>44977</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 41581-2023</t>
+          <t>A 20685-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45173</v>
+        <v>45436</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1873,7 +1873,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19794-2023</t>
+          <t>A 20684-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45051</v>
+        <v>45436</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 63886-2023</t>
+          <t>A 40154-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45278</v>
+        <v>45894</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2019,7 +2019,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 40154-2025</t>
+          <t>A 8469-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45894</v>
+        <v>44977</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2092,7 +2092,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 41395-2025</t>
+          <t>A 35135-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45901</v>
+        <v>45852</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2165,7 +2165,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 42471-2025</t>
+          <t>A 35139-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45905</v>
+        <v>45852</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2238,7 +2238,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 43151-2025</t>
+          <t>A 41395-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45910</v>
+        <v>45901</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2311,7 +2311,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 20685-2024</t>
+          <t>A 35640-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45436</v>
+        <v>45859</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 44022-2025</t>
+          <t>A 42471-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45915</v>
+        <v>45905</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 48403-2024</t>
+          <t>A 43151-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45590</v>
+        <v>45910</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2530,7 +2530,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60262-2024</t>
+          <t>A 44022-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45642</v>
+        <v>45915</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 60265-2024</t>
+          <t>A 15108-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45642</v>
+        <v>45016</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 53423-2023</t>
+          <t>A 60265-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45229</v>
+        <v>45642</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2749,7 +2749,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 48153-2025</t>
+          <t>A 53423-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45933</v>
+        <v>45229</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2822,7 +2822,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60255-2024</t>
+          <t>A 60262-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2839,7 +2839,7 @@
         <v>45642</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 34623-2025</t>
+          <t>A 60255-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45847</v>
+        <v>45642</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 35139-2025</t>
+          <t>A 48153-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45852</v>
+        <v>45933</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3041,7 +3041,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 35135-2025</t>
+          <t>A 34623-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45852</v>
+        <v>45847</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.1</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35640-2025</t>
+          <t>A 43028-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3124,14 +3124,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45859</v>
+        <v>45182</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3187,7 +3187,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37149-2023</t>
+          <t>A 54366-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45155</v>
+        <v>45965</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3260,7 +3260,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 15108-2023</t>
+          <t>A 13239-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45016</v>
+        <v>45386</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3333,7 +3333,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54366-2025</t>
+          <t>A 57530-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45965</v>
+        <v>45980</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3406,7 +3406,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 43028-2023</t>
+          <t>A 57532-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3416,14 +3416,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45182</v>
+        <v>45980</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 3588-2026</t>
+          <t>A 22465-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46042</v>
+        <v>46155</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>10.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 57532-2025</t>
+          <t>A 22411-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45980</v>
+        <v>46154</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57530-2025</t>
+          <t>A 10579-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45980</v>
+        <v>45366</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3698,7 +3698,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2269-2025</t>
+          <t>A 22407-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45673</v>
+        <v>46154</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3771,7 +3771,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8469-2023</t>
+          <t>A 3408-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3781,14 +3781,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44977</v>
+        <v>45319</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7509-2026</t>
+          <t>A 37583-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3858,10 +3858,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46059</v>
+        <v>45541</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3917,7 +3917,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7506-2026</t>
+          <t>A 58789-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46059</v>
+        <v>44903</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8328-2026</t>
+          <t>A 58794-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46064</v>
+        <v>44903</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4063,7 +4063,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9149-2026</t>
+          <t>A 13250-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46070</v>
+        <v>45386</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 10350-2026</t>
+          <t>A 3588-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46076</v>
+        <v>46042</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4209,7 +4209,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 10217-2026</t>
+          <t>A 59223-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4219,14 +4219,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46076</v>
+        <v>44899</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12186-2026</t>
+          <t>A 2269-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46086</v>
+        <v>45673</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4355,7 +4355,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12109-2026</t>
+          <t>A 7506-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4369,10 +4369,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46086</v>
+        <v>46059</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>9.199999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4428,7 +4428,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 12532-2026</t>
+          <t>A 7509-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46090</v>
+        <v>46059</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4501,7 +4501,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 12523-2026</t>
+          <t>A 8328-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46090</v>
+        <v>46064</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14123-2026</t>
+          <t>A 9149-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46099</v>
+        <v>46070</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4647,7 +4647,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 16233-2026</t>
+          <t>A 52-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46111</v>
+        <v>45293</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4720,7 +4720,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 16607-2026</t>
+          <t>A 10217-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4730,14 +4730,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46112</v>
+        <v>46076</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4793,7 +4793,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 58793-2022</t>
+          <t>A 10350-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4807,10 +4807,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44903</v>
+        <v>46076</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4866,7 +4866,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 18831-2026</t>
+          <t>A 44146-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46128</v>
+        <v>45188</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4939,7 +4939,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 19309-2026</t>
+          <t>A 22605-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4949,14 +4949,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46133</v>
+        <v>45789</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44536-2024</t>
+          <t>A 63886-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45574</v>
+        <v>45278</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5085,7 +5085,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 37583-2024</t>
+          <t>A 12186-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45541</v>
+        <v>46086</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 22411-2026</t>
+          <t>A 12109-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46154</v>
+        <v>46086</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5231,7 +5231,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 22407-2026</t>
+          <t>A 12532-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46154</v>
+        <v>46090</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5304,7 +5304,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 22465-2026</t>
+          <t>A 12523-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46155</v>
+        <v>46090</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>10.4</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5377,7 +5377,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 61991-2024</t>
+          <t>A 58619-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45653</v>
+        <v>45635</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5450,7 +5450,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 37077-2023</t>
+          <t>A 19794-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5464,10 +5464,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45155</v>
+        <v>45051</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5523,7 +5523,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 44146-2023</t>
+          <t>A 14123-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45188</v>
+        <v>46099</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5596,7 +5596,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58789-2022</t>
+          <t>A 16607-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5610,10 +5610,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44903</v>
+        <v>46112</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 58794-2022</t>
+          <t>A 16233-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44903</v>
+        <v>46111</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5742,7 +5742,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 20683-2024</t>
+          <t>A 18831-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5756,10 +5756,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45436</v>
+        <v>46128</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5815,7 +5815,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 59223-2022</t>
+          <t>A 19309-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44899</v>
+        <v>46133</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8464-2023</t>
+          <t>A 22793-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5902,10 +5902,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44977</v>
+        <v>46157</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5961,7 +5961,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 60969-2021</t>
+          <t>A 31834-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44497</v>
+        <v>46230</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 22793-2026</t>
+          <t>A 37077-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6048,10 +6048,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46157</v>
+        <v>45155</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 20684-2024</t>
+          <t>A 48403-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45436</v>
+        <v>45590</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 31834-2026</t>
+          <t>A 13246-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6194,10 +6194,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46230</v>
+        <v>45386</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6253,7 +6253,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13239-2024</t>
+          <t>A 32827-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45386</v>
+        <v>46243</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6326,7 +6326,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39085-2023</t>
+          <t>A 44536-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45164</v>
+        <v>45574</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6399,7 +6399,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 440-2023</t>
+          <t>A 8464-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44929</v>
+        <v>44977</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6472,7 +6472,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 8474-2023</t>
+          <t>A 37149-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6486,10 +6486,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44977</v>
+        <v>45155</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6562,7 +6562,7 @@
         <v>45761</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>45761</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>45761</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 32827-2026</t>
+          <t>A 60969-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46243</v>
+        <v>44497</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6837,7 +6837,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 13250-2024</t>
+          <t>A 42006-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45386</v>
+        <v>46303</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6910,7 +6910,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3408-2024</t>
+          <t>A 20683-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6920,14 +6920,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45319</v>
+        <v>45436</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52-2024</t>
+          <t>A 35402-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6997,10 +6997,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45293</v>
+        <v>46261</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7056,7 +7056,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 42006-2026</t>
+          <t>A 35911-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46303</v>
+        <v>46266</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7085,8 +7085,13 @@
           <t>LYSEKIL</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>6.2</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7129,7 +7134,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 35402-2026</t>
+          <t>A 42964-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7143,10 +7148,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46261</v>
+        <v>46310</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7159,7 +7164,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7202,7 +7207,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 42964-2026</t>
+          <t>A 42968-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7219,7 +7224,7 @@
         <v>46310</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7232,7 +7237,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7275,7 +7280,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 42968-2026</t>
+          <t>A 440-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7289,10 +7294,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46310</v>
+        <v>44929</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7305,7 +7310,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7348,7 +7353,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 35911-2026</t>
+          <t>A 39085-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7362,10 +7367,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46266</v>
+        <v>45164</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7377,13 +7382,8 @@
           <t>LYSEKIL</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7443,7 +7443,7 @@
         <v>45006</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>

--- a/Översikt LYSEKIL.xlsx
+++ b/Översikt LYSEKIL.xlsx
@@ -601,7 +601,7 @@
         <v>45860</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>44675</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 53422-2023</t>
+        